--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Java Full Stack Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Westbrook Partners</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=299ffa44541b6cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Westbrook Partners</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
+          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4fa506997c9d91</t>
         </is>
       </c>
     </row>
@@ -688,7 +688,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4fa506997c9d91</t>
+          <t>https://www.indeed.com/viewjob?jk=e97a7a884716018a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
+          <t>Product Owner - Cloud Contact Center (CCaaS) &amp; Data Platform</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, SQS, SNS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97a7a884716018a</t>
+          <t>https://www.indeed.com/viewjob?jk=83ea14ffde25c4ae</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Product Owner - Cloud Contact Center (CCaaS) &amp; Data Platform</t>
+          <t>Sr. Data Engineer - AI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>Dairy Farmers of America, Inc.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, SQS, SNS, IAM, RDS, Azure, Data Factory</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ea14ffde25c4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
         </is>
       </c>
     </row>
@@ -1063,17 +1063,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Software Development - Cloud Platform</t>
+          <t>Senior Data Modeler - Mongo DB</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Kanan solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,69 +1081,69 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999c2fd6b4078473</t>
+          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development - Cloud Platform</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, ECS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=999c2fd6b4078473</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>Kind Lending</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176a7564b0c762a0</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777f4483805c8d79</t>
+          <t>https://www.indeed.com/viewjob?jk=176a7564b0c762a0</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9bb3ce748cacccb</t>
+          <t>https://www.indeed.com/viewjob?jk=777f4483805c8d79</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=d9bb3ce748cacccb</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Analytics Engineer I</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Analytics Engineer I</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Governance</t>
+          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a3de99cc55670f</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Solutions Architect - Data Governance</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>SHI International</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
+          <t>https://www.indeed.com/viewjob?jk=d9a3de99cc55670f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Operations Scientist, Development</t>
+          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Operations Scientist, Development</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Group Technical Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cabd49f3b0af0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Group Technical Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=0cabd49f3b0af0ce</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682458f658094e85</t>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e9c649072734ae</t>
+          <t>https://www.indeed.com/viewjob?jk=682458f658094e85</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580cc59935f51044</t>
+          <t>https://www.indeed.com/viewjob?jk=88e9c649072734ae</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=580cc59935f51044</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,19 +2456,19 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ad7b2e04ae0cc7</t>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Key2Source INC</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala, Kafka</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f6b132222bc4dce</t>
+          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Key2Source INC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,14 +2561,14 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>NetSPI</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, GitHub Actions, Docker, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=6aa161d158387111</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>NetSPI</t>
+          <t>Central One Federal Credit Union</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Shrewsbury, MA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, GitHub Actions, Docker, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa161d158387111</t>
+          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Central One Federal Credit Union</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Shrewsbury, MA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Technical Product Owner, Data and Payment Technology</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2770,41 +2770,6 @@
         </is>
       </c>
       <c r="G67" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Princess</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Fort Lauderdale, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D68" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>RDS, Databricks, HDFS, Hive, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
+          <t>https://www.indeed.com/viewjob?jk=9dca464379b2183e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
+          <t>Software Engineer, Core Platform</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
+          <t>https://www.indeed.com/viewjob?jk=363f4f316481e53f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>Software Engineer, Core Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=5742b1eac2e5457a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Westbrook Partners</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
+          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4fa506997c9d91</t>
+          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
+          <t>senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97a7a884716018a</t>
+          <t>https://www.indeed.com/viewjob?jk=5b5061b072e1bbd6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Product Owner - Cloud Contact Center (CCaaS) &amp; Data Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>Westbrook Partners</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, SQS, SNS, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ea14ffde25c4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - AI</t>
+          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Dairy Farmers of America, Inc.</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Snowflake Developer – Python &amp; SQL Server</t>
+          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unitedone health</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4fa506997c9d91</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
+          <t>https://www.indeed.com/viewjob?jk=e97a7a884716018a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Product Owner - Cloud Contact Center (CCaaS) &amp; Data Platform</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>13.9</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, SQS, SNS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=83ea14ffde25c4ae</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Sr. Data Engineer - AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Dairy Farmers of America, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
+          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Snowflake Developer – Python &amp; SQL Server</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Unitedone health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
+          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Mongo DB</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kanan solutions</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
+          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Development - Cloud Platform</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999c2fd6b4078473</t>
+          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Data Modeler - Mongo DB</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>Kanan solutions</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development - Cloud Platform</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, Kinesis, ECS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=999c2fd6b4078473</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kind Lending</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176a7564b0c762a0</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777f4483805c8d79</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9bb3ce748cacccb</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=176a7564b0c762a0</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Analytics Engineer I</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+          <t>https://www.indeed.com/viewjob?jk=777f4483805c8d79</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=d9bb3ce748cacccb</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Analytics Engineer I</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Solutions Architect - Data Governance</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SHI International</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, Snowflake, SQL Server, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9a3de99cc55670f</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,19 +1966,19 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Operations Scientist, Development</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -1987,11 +1987,11 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Group Technical Architect</t>
+          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cabd49f3b0af0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Data Operations Scientist, Development</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682458f658094e85</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e9c649072734ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580cc59935f51044</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Marcus &amp; Millichap</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Group Technical Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=0cabd49f3b0af0ce</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Key2Source INC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=682458f658094e85</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Security Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=88e9c649072734ae</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NetSPI</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, PostgreSQL, GitHub Actions, Docker, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6aa161d158387111</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Central One Federal Credit Union</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Shrewsbury, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
+          <t>IAR Senior Data Analyst</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,15 +2761,295 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=014c35a8d1bc95ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Ab Initio Developer</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Key2Source INC</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Central One Federal Credit Union</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Shrewsbury, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>X Development</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Associate Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Technical Product Owner, Data and Payment Technology</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Princess</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
+          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Kind Lending</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1903,17 +1903,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,17 +2096,17 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
         </is>
       </c>
     </row>
@@ -2183,17 +2183,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Operations Scientist, Development</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Scientist, Development</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
@@ -2568,25 +2568,25 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88e9c649072734ae</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>IAR Senior Data Analyst</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>Western Governors University</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=014c35a8d1bc95ce</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>IAR Senior Data Analyst</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Key2Source INC</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=014c35a8d1bc95ce</t>
+          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Key2Source INC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Product Owner, Data and Payment Technology</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Central One Federal Credit Union</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Shrewsbury, MA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>Central One Federal Credit Union</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Shrewsbury, MA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
         </is>
       </c>
     </row>
@@ -3017,41 +3017,6 @@
       <c r="G74" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Princess</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Fort Lauderdale, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
+          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
@@ -1273,17 +1273,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>Kind Lending</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176a7564b0c762a0</t>
+          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777f4483805c8d79</t>
+          <t>https://www.indeed.com/viewjob?jk=176a7564b0c762a0</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9bb3ce748cacccb</t>
+          <t>https://www.indeed.com/viewjob?jk=777f4483805c8d79</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=d9bb3ce748cacccb</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>TrueScripts Management Services</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>Washington, IN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Analytics Engineer I</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Analytics Engineer I</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Data Scientist, Development</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Scientist, Development</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Group Technical Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cabd49f3b0af0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Marcus &amp; Millichap</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Group Technical Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=0cabd49f3b0af0ce</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Security Engineer</t>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>NewYork-Presbyterian Hospital</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, SQS, SNS, Azure, Event Hubs, GCP, Scala, Power BI, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=682458f658094e85</t>
+          <t>https://www.indeed.com/viewjob?jk=1343552027471cbf</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,32 +2596,32 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>IAR Senior Data Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Western Governors University</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Snowflake Schema, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=014c35a8d1bc95ce</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Key2Source INC</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Central One Federal Credit Union</t>
+          <t>Key2Source INC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Shrewsbury, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>Central One Federal Credit Union</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Shrewsbury, MA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,7 +3016,112 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Technical Product Owner, Data and Payment Technology</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Princess</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer, Core Platform</t>
+          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,7 +521,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363f4f316481e53f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5742b1eac2e5457a</t>
+          <t>https://www.indeed.com/viewjob?jk=363f4f316481e53f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
+          <t>Software Engineer, Core Platform</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
+          <t>https://www.indeed.com/viewjob?jk=5742b1eac2e5457a</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=e5793d31b52a070a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>Kind Lending</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
@@ -1658,25 +1658,25 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>TrueScripts Management Services</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Washington, IN, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Java Full Stack Software Engineer II - React / PostgreSQL</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf14fb387b368af</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>TrueScripts Management Services</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>Washington, IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Analytics Engineer I</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Analytics Engineer I</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Scientist, Development</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Data Scientist, Development</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Group Technical Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cabd49f3b0af0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>NewYork-Presbyterian Hospital</t>
+          <t>Marcus &amp; Millichap</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1343552027471cbf</t>
+          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Group Technical Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=0cabd49f3b0af0ce</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Senior Data &amp; AI Analyst, Finance Systems</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>AeroVironment</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Simi Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Oracle, Power BI, Tableau, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=01ab4083a3713e89</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>NewYork-Presbyterian Hospital</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=1343552027471cbf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Key2Source INC</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Central One Federal Credit Union</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Shrewsbury, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>Key2Source INC</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>Central One Federal Credit Union</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Shrewsbury, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,15 +3111,120 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Technical Product Owner, Data and Payment Technology</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Princess</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Bank of America</t>
+          <t>BioAgilytix Labs</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>19.4</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RDS, Databricks, HDFS, Hive, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
+          <t>AWS, Glue, Lambda, S3, ECS, RDS, Azure, Medallion Architecture, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dca464379b2183e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f99a8f1166781f9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Bank of America</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>RDS, Databricks, HDFS, Hive, Spark, Scala, Kafka, Snowflake, Oracle, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,7 +531,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
+          <t>https://www.indeed.com/viewjob?jk=9dca464379b2183e</t>
         </is>
       </c>
     </row>
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
+          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>senior Data Engineer</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5061b072e1bbd6</t>
+          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Westbrook Partners</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b5061b072e1bbd6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Westbrook Partners</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
+          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
+          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4fa506997c9d91</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97a7a884716018a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd4fa506997c9d91</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Product Owner - Cloud Contact Center (CCaaS) &amp; Data Platform</t>
+          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>AbbVie</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Worcester, MA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, SQS, SNS, IAM, RDS, Azure, Data Factory</t>
+          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ea14ffde25c4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e97a7a884716018a</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - AI</t>
+          <t>Product Owner - Cloud Contact Center (CCaaS) &amp; Data Platform</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dairy Farmers of America, Inc.</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, SQS, SNS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
+          <t>https://www.indeed.com/viewjob?jk=83ea14ffde25c4ae</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Snowflake Developer – Python &amp; SQL Server</t>
+          <t>Sr. Data Engineer - AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unitedone health</t>
+          <t>Dairy Farmers of America, Inc.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
+          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Snowflake Developer – Python &amp; SQL Server</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>Unitedone health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
+          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
+          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
+          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
+          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Mongo DB</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Kanan solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Development - Cloud Platform</t>
+          <t>Senior Data Modeler - Mongo DB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Kanan solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,29 +1256,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999c2fd6b4078473</t>
+          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development - Cloud Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1287,73 +1287,73 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, ECS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5793d31b52a070a</t>
+          <t>https://www.indeed.com/viewjob?jk=999c2fd6b4078473</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Lynden</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>SeaTac, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e5793d31b52a070a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>Kind Lending</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176a7564b0c762a0</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777f4483805c8d79</t>
+          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9bb3ce748cacccb</t>
+          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=176a7564b0c762a0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Java Full Stack Software Engineer II - React / PostgreSQL</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf14fb387b368af</t>
+          <t>https://www.indeed.com/viewjob?jk=777f4483805c8d79</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TrueScripts Management Services</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Washington, IN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+          <t>https://www.indeed.com/viewjob?jk=d9bb3ce748cacccb</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Java Full Stack Software Engineer II - React / PostgreSQL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=0bf14fb387b368af</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>TrueScripts Management Services</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>Washington, IN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer I</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Analytics Engineer I</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
+          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist, Development</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Data Scientist, Development</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Group Technical Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cabd49f3b0af0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Analyst, Finance Systems</t>
+          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AeroVironment</t>
+          <t>Marcus &amp; Millichap</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Simi Valley, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Power BI, Tableau, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ab4083a3713e89</t>
+          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+          <t>Group Technical Architect</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NewYork-Presbyterian Hospital</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
+          <t>Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1343552027471cbf</t>
+          <t>https://www.indeed.com/viewjob?jk=0cabd49f3b0af0ce</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Senior Data &amp; AI Analyst, Finance Systems</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>AeroVironment</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Simi Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Oracle, Power BI, Tableau, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=01ab4083a3713e89</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>NewYork-Presbyterian Hospital</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=1343552027471cbf</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Key2Source INC</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Central One Federal Credit Union</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Shrewsbury, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Key2Source INC</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>Central One Federal Credit Union</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Shrewsbury, MA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,15 +3216,85 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Technical Product Owner, Data and Payment Technology</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Princess</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer, Core Platform</t>
+          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363f4f316481e53f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5742b1eac2e5457a</t>
+          <t>https://www.indeed.com/viewjob?jk=363f4f316481e53f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
+          <t>Software Engineer, Core Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
+          <t>https://www.indeed.com/viewjob?jk=5742b1eac2e5457a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
+          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Kind Lending</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5793d31b52a070a</t>
+          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=e5793d31b52a070a</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=176a7564b0c762a0</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176a7564b0c762a0</t>
+          <t>https://www.indeed.com/viewjob?jk=777f4483805c8d79</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777f4483805c8d79</t>
+          <t>https://www.indeed.com/viewjob?jk=d9bb3ce748cacccb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9bb3ce748cacccb</t>
+          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Java Full Stack Software Engineer II - React / PostgreSQL</t>
+          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Data Modeling, Splunk</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0bf14fb387b368af</t>
+          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
         </is>
       </c>
     </row>
@@ -1803,12 +1803,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>TrueScripts Management Services</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Washington, IN, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>TrueScripts Management Services</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Washington, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Analytics Engineer I</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Analytics Engineer I</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
+          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Scientist, Development</t>
+          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,19 +2596,19 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
+          <t>Data Scientist, Development</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Group Technical Architect</t>
+          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Marcus &amp; Millichap</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cabd49f3b0af0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Analyst, Finance Systems</t>
+          <t>Group Technical Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AeroVironment</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Simi Valley, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Power BI, Tableau, CI/CD, Git, Python, SQL</t>
+          <t>Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ab4083a3713e89</t>
+          <t>https://www.indeed.com/viewjob?jk=0cabd49f3b0af0ce</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+          <t>Senior Data &amp; AI Analyst, Finance Systems</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>NewYork-Presbyterian Hospital</t>
+          <t>AeroVironment</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Simi Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Oracle, Power BI, Tableau, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1343552027471cbf</t>
+          <t>https://www.indeed.com/viewjob?jk=01ab4083a3713e89</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>NewYork-Presbyterian Hospital</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=1343552027471cbf</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Key2Source INC</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Central One Federal Credit Union</t>
+          <t>Key2Source INC</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Shrewsbury, MA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Central One Federal Credit Union</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Shrewsbury, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,14 +3191,14 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,15 +3286,50 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Technical Product Owner, Data and Payment Technology</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Princess</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
           <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G83"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
+          <t>Software Engineer, Core Platform</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
+          <t>https://www.indeed.com/viewjob?jk=363f4f316481e53f</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363f4f316481e53f</t>
+          <t>https://www.indeed.com/viewjob?jk=5742b1eac2e5457a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, Core Platform</t>
+          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5742b1eac2e5457a</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
+          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
@@ -1343,17 +1343,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
+          <t>https://www.indeed.com/viewjob?jk=e5793d31b52a070a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>Kind Lending</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5793d31b52a070a</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176a7564b0c762a0</t>
+          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=777f4483805c8d79</t>
+          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d9bb3ce748cacccb</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>TrueScripts Management Services</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Washington, IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TrueScripts Management Services</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Washington, IN, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Analytics Engineer I</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Analytics Engineer I</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
+          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Data Scientist, Development</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Marcus &amp; Millichap</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Group Technical Architect</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>HCLTech</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=0cabd49f3b0af0ce</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Scientist, Development</t>
+          <t>Senior Data &amp; AI Analyst, Finance Systems</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>AeroVironment</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Simi Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>AWS, RDS, Azure, Oracle, Power BI, Tableau, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=01ab4083a3713e89</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>NewYork-Presbyterian Hospital</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Manhattan, NY, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
+          <t>https://www.indeed.com/viewjob?jk=1343552027471cbf</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Group Technical Architect</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL, ELT</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cabd49f3b0af0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Analyst, Finance Systems</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AeroVironment</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Simi Valley, CA, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Power BI, Tableau, CI/CD, Git, Python, SQL</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ab4083a3713e89</t>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>NewYork-Presbyterian Hospital</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1343552027471cbf</t>
+          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Sr Engineer - MLOps Platform</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Central One Federal Credit Union</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Shrewsbury, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Key2Source INC</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Central One Federal Credit Union</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Shrewsbury, MA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,14 +3156,14 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Product Owner, Data and Payment Technology</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Key2Source INC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,77 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Associate Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Princess</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Fort Lauderdale, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
+          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,52 +958,52 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Snowflake Developer – Python &amp; SQL Server</t>
+          <t>Senior SAP Sales and Service Cloud Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unitedone health</t>
+          <t>Data Solutions LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
+          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
+          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Snowflake Developer – Python &amp; SQL Server</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Unitedone health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
+          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Mongo DB</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kanan solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
+          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Development - Cloud Platform</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999c2fd6b4078473</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Modeler - Mongo DB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lynden</t>
+          <t>Kanan solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SeaTac, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,29 +1326,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
+          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development - Cloud Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1357,73 +1357,73 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, ECS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5793d31b52a070a</t>
+          <t>https://www.indeed.com/viewjob?jk=999c2fd6b4078473</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Lynden</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>SeaTac, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>Kind Lending</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,14 +1686,14 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
+          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
         </is>
       </c>
     </row>
@@ -1733,12 +1733,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TrueScripts Management Services</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Washington, IN, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>TrueScripts Management Services</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Washington, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Analytics Engineer I</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Analytics Engineer I</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Senior ML/Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Catapult Sports</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist, Development</t>
+          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Scientist, Development</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Group Technical Architect</t>
+          <t>Senior Data &amp; AI Analyst, Finance Systems</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HCLTech</t>
+          <t>AeroVironment</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Simi Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Azure, Databricks, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Oracle, Power BI, Tableau, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cabd49f3b0af0ce</t>
+          <t>https://www.indeed.com/viewjob?jk=01ab4083a3713e89</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Analyst, Finance Systems</t>
+          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AeroVironment</t>
+          <t>Marcus &amp; Millichap</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Simi Valley, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Power BI, Tableau, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ab4083a3713e89</t>
+          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>NewYork-Presbyterian Hospital</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Manhattan, NY, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1343552027471cbf</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Sr Engineer - MLOps Platform</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Engineer - MLOps Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Central One Federal Credit Union</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Shrewsbury, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
+          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Central One Federal Credit Union</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Shrewsbury, MA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Technical Product Owner, Data and Payment Technology</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>Key2Source INC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3225,41 +3225,6 @@
         </is>
       </c>
       <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Ab Initio Developer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Key2Source INC</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Wright-Patterson AFB, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,34 +2236,34 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior ML/Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Catapult Sports</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,17 +2271,17 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, SNS, ECS, RDS, Spark, Scala, Spark Streaming</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f70070de74edaf0a</t>
+          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
         </is>
       </c>
     </row>
@@ -2323,25 +2323,25 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Business Analyst – Data Analytics, Visualization &amp; AI Solutions</t>
+          <t>Data Scientist, Development</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Vertex AI, Scala, Data Modeling, Power BI</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e58ddd60612b0a2</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Scientist, Development</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data &amp; AI Analyst, Finance Systems</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>AeroVironment</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Simi Valley, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, Oracle, Power BI, Tableau, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=01ab4083a3713e89</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Analyst, Finance Systems</t>
+          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AeroVironment</t>
+          <t>Marcus &amp; Millichap</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Simi Valley, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,34 +2586,34 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Power BI, Tableau, CI/CD, Git, Python, SQL</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ab4083a3713e89</t>
+          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Sr Engineer - MLOps Platform</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Engineer - MLOps Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Central One Federal Credit Union</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Shrewsbury, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
+          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Central One Federal Credit Union</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Shrewsbury, MA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,14 +3016,14 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Technical Product Owner, Data and Payment Technology</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>Key2Source INC</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3190,41 +3190,6 @@
         </is>
       </c>
       <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Ab Initio Developer</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>Key2Source INC</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G79"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Engineer, Core Platform</t>
+          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,7 +566,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363f4f316481e53f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
         </is>
       </c>
     </row>
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,24 +601,24 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5742b1eac2e5457a</t>
+          <t>https://www.indeed.com/viewjob?jk=363f4f316481e53f</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
+          <t>Software Engineer, Core Platform</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>KONG</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Olympia, WA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
+          <t>https://www.indeed.com/viewjob?jk=5742b1eac2e5457a</t>
         </is>
       </c>
     </row>
@@ -958,60 +958,60 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior SAP Sales and Service Cloud Consultant</t>
+          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Data Solutions LLC</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior SAP Sales and Service Cloud Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Data Solutions LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Snowflake Developer – Python &amp; SQL Server</t>
+          <t>Data Engineer IV (6281)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unitedone health</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>RDS, BigQuery, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
+          <t>https://www.indeed.com/viewjob?jk=2638fbb6172c3dae</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
+          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
+          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Snowflake Developer – Python &amp; SQL Server</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Unitedone health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
+          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Mongo DB</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kanan solutions</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
+          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Development - Cloud Platform</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999c2fd6b4078473</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Modeler - Mongo DB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lynden</t>
+          <t>Kanan solutions</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SeaTac, WA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,104 +1396,104 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
+          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Development - Cloud Platform</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Kinesis, ECS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=999c2fd6b4078473</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>Lynden</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>SeaTac, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>Kind Lending</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
@@ -1593,12 +1593,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
+          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TrueScripts Management Services</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Washington, IN, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>TrueScripts Management Services</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>Washington, IN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Analytics Engineer I</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Analytics Engineer I</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Wright-Patterson AFB, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Wright-Patterson AFB, OH, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,34 +2271,34 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,42 +2306,42 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Scientist, Development</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Data Scientist, Development</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Data &amp; AI Analyst, Finance Systems</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>AeroVironment</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Simi Valley, CA, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, Power BI, Tableau, CI/CD, Git, Python, SQL</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01ab4083a3713e89</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Sr Database Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, Terraform</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd582173f03bef9</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Marcus &amp; Millichap</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Senior.Net Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Richardson, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Data Engineer - Data Quality and Governance</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Engineer - MLOps Platform</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Central One Federal Credit Union</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Shrewsbury, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Engineer - MLOps Platform</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Central One Federal Credit Union</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Shrewsbury, MA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
         </is>
       </c>
     </row>
@@ -3128,17 +3128,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Key2Source INC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,15 +3181,120 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Technical Product Owner, Data and Payment Technology</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Princess</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Fort Lauderdale, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Ab Initio Developer</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Key2Source INC</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
           <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
+          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
         </is>
       </c>
     </row>
@@ -818,17 +818,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
+          <t>Product Owner - Cloud Contact Center (CCaaS) &amp; Data Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>AWS, Glue, Lambda, Redshift, SQS, SNS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd4fa506997c9d91</t>
+          <t>https://www.indeed.com/viewjob?jk=83ea14ffde25c4ae</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Associate Scientific Technical Engineer II, PDS&amp;T CMC</t>
+          <t>Sr. Data Engineer - AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AbbVie</t>
+          <t>Dairy Farmers of America, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Worcester, MA, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97a7a884716018a</t>
+          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Product Owner - Cloud Contact Center (CCaaS) &amp; Data Platform</t>
+          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, SQS, SNS, IAM, RDS, Azure, Data Factory</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,102 +916,102 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ea14ffde25c4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - AI</t>
+          <t>Senior SAP Sales and Service Cloud Consultant</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Dairy Farmers of America, Inc.</t>
+          <t>Data Solutions LLC</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
+          <t>Data Engineer IV (6281)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
+          <t>RDS, BigQuery, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2638fbb6172c3dae</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior SAP Sales and Service Cloud Consultant</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Data Solutions LLC</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,59 +1021,59 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
+          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer IV (6281)</t>
+          <t>Snowflake Developer – Python &amp; SQL Server</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Unitedone health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2638fbb6172c3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
+          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Snowflake Developer – Python &amp; SQL Server</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unitedone health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,24 +1126,24 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
+          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
+          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
+          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Modeler - Mongo DB</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kanan solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Development - Cloud Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, Kinesis, ECS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=999c2fd6b4078473</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Mongo DB</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kanan solutions</t>
+          <t>Lynden</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>SeaTac, WA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,104 +1396,104 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Development - Cloud Platform</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Kind Lending</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999c2fd6b4078473</t>
+          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Lynden</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>SeaTac, WA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>TrueScripts Management Services</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Washington, IN, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>TrueScripts Management Services</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Washington, IN, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer I</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Analytics Engineer I</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Senior Enterprise Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>Native American Industrial Solutions, LLC (NAIS)</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wright-Patterson AFB, OH, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wright-Patterson AFB, OH, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,34 +2306,34 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Scientist, Development</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Data Scientist, Development</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Marcus &amp; Millichap</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
         </is>
       </c>
     </row>
@@ -2638,17 +2638,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior.Net Full-Stack Engineer</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Richardson, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, SQL Server, CI/CD, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24927959bc1c9207</t>
+          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Senior Data Engineer - Data Quality and Governance</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Quality and Governance</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Sr Engineer - MLOps Platform</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>Central One Federal Credit Union</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Shrewsbury, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr Engineer - MLOps Platform</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Central One Federal Credit Union</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Shrewsbury, MA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technical Product Owner, Data and Payment Technology</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Key2Source INC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3225,76 +3225,6 @@
         </is>
       </c>
       <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Princess</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Fort Lauderdale, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Ab Initio Developer</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Key2Source INC</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
+          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
         </is>
       </c>
     </row>
@@ -1238,17 +1238,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
@@ -1413,17 +1413,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>Kind Lending</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
@@ -2358,17 +2358,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Data Scientist, Development</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Scientist, Development</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
+          <t>Sr Database Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd582173f03bef9</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr Database Engineer</t>
+          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Marcus &amp; Millichap</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd582173f03bef9</t>
+          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
         </is>
       </c>
     </row>
@@ -2778,17 +2778,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr Engineer - MLOps Platform</t>
+          <t>Azure Databricks/Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>signitives IT Solutions</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
+          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Engineer - MLOps Platform</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Central One Federal Credit Union</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Shrewsbury, MA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Central One Federal Credit Union</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Shrewsbury, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Technical Product Owner, Data and Payment Technology</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Key2Source INC</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,15 +3216,50 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Ab Initio Developer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Key2Source INC</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
           <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G81"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
+          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Engineer, Core Platform</t>
+          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=363f4f316481e53f</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer, Core Platform</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Olympia, WA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Kafka, DynamoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5742b1eac2e5457a</t>
+          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
+          <t>senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Spark, Scala, Oracle</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
+          <t>https://www.indeed.com/viewjob?jk=5b5061b072e1bbd6</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Westbrook Partners</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>senior Data Engineer</t>
+          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5061b072e1bbd6</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Product Owner - Cloud Contact Center (CCaaS) &amp; Data Platform</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Westbrook Partners</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Redshift, SQS, SNS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=83ea14ffde25c4ae</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
+          <t>Sr. Data Engineer - AI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Dairy Farmers of America, Inc.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
+          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Product Owner - Cloud Contact Center (CCaaS) &amp; Data Platform</t>
+          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, SQS, SNS, IAM, RDS, Azure, Data Factory</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,102 +846,102 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ea14ffde25c4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - AI</t>
+          <t>Senior SAP Sales and Service Cloud Consultant</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dairy Farmers of America, Inc.</t>
+          <t>Data Solutions LLC</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
+          <t>Data Engineer IV (6281)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
+          <t>RDS, BigQuery, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
+          <t>https://www.indeed.com/viewjob?jk=2638fbb6172c3dae</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior SAP Sales and Service Cloud Consultant</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Data Solutions LLC</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
+          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer IV (6281)</t>
+          <t>Snowflake Developer – Python &amp; SQL Server</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>Unitedone health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2638fbb6172c3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
+          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Snowflake Developer – Python &amp; SQL Server</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unitedone health</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
+          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
+          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
+          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Modeler - Mongo DB</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kanan solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Development - Cloud Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Oak Brook, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, Kinesis, ECS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-15</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=999c2fd6b4078473</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Mongo DB</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Kanan solutions</t>
+          <t>Lynden</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>SeaTac, WA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,104 +1326,104 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Software Development - Cloud Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999c2fd6b4078473</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Lynden</t>
+          <t>Kind Lending</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SeaTac, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
+          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
@@ -1523,12 +1523,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>TrueScripts Management Services</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Washington, IN, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TrueScripts Management Services</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Washington, IN, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer I</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Azure IoT Solutions Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Bio-Tech Lab Services, LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Analytics Engineer I</t>
+          <t>Senior Enterprise Architect</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Native American Industrial Solutions, LLC (NAIS)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0da3224c8b4b5fcc</t>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Enterprise Architect</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Native American Industrial Solutions, LLC (NAIS)</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,17 +2026,17 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
+          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
         </is>
       </c>
     </row>
@@ -2048,12 +2048,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Wright-Patterson AFB, OH, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
+          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Wright-Patterson AFB, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
+          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Data Scientist, Development</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Data Quality Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Insperity</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Kingwood, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,59 +2316,59 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Data Engineer- Greater Tampa</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Scientist, Development</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Marcus &amp; Millichap</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr Database Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, Terraform</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd582173f03bef9</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Sr Database Engineer</t>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Woongjin, Inc</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, Terraform</t>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,24 +2596,24 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd582173f03bef9</t>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
+          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Application Security Engineer IV</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Edward Jones</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Tempe, AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Senior Data Engineer - Data Quality and Governance</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Quality and Governance</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Sr Engineer - MLOps Platform</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Azure Databricks/Data Engineer</t>
+          <t>Contract Full-Stack Developer - existing application completion &amp; deployment</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>signitives IT Solutions</t>
+          <t>NICA</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Falmouth, MA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark, PySpark, Scala, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4541db046ada0e3f</t>
+          <t>https://www.indeed.com/viewjob?jk=1624bcb33518b242</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr Engineer - MLOps Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Central One Federal Credit Union</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Shrewsbury, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
+          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Central One Federal Credit Union</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Shrewsbury, MA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Associate Solutions Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>540</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,14 +3086,14 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Schaumburg, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Technical Product Owner, Data and Payment Technology</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>Princess</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Fort Lauderdale, FL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>Key2Source INC</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3225,41 +3225,6 @@
         </is>
       </c>
       <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Ab Initio Developer</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>Key2Source INC</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:G126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Veridic Solutions</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, Redshift, Azure, Synapse Analytics, BigQuery, Scala, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=5dc73ec2502e27a3</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>senior Data Engineer</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5061b072e1bbd6</t>
+          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Westbrook Partners</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b5061b072e1bbd6</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Westbrook Partners</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,24 +741,24 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
+          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Product Owner - Cloud Contact Center (CCaaS) &amp; Data Platform</t>
+          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,7 +766,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, SQS, SNS, IAM, RDS, Azure, Data Factory</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ea14ffde25c4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - AI</t>
+          <t>Product Owner - Cloud Contact Center (CCaaS) &amp; Data Platform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dairy Farmers of America, Inc.</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, SQS, SNS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
+          <t>https://www.indeed.com/viewjob?jk=83ea14ffde25c4ae</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
+          <t>Sr. Data Engineer - AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>Dairy Farmers of America, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,67 +846,67 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
+          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior SAP Sales and Service Cloud Consultant</t>
+          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Data Solutions LLC</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer IV (6281)</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Scala, Oracle, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2638fbb6172c3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=da5d92ba9e6d3e13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Data Engineer IV (6281)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>itD Tech</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
+          <t>RDS, BigQuery, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
+          <t>https://www.indeed.com/viewjob?jk=2638fbb6172c3dae</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Snowflake Developer – Python &amp; SQL Server</t>
+          <t>Senior SAP Sales and Service Cloud Consultant</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unitedone health</t>
+          <t>Data Solutions LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Palantir Data engineer - Forward Deployment Engineers</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>AI SPINS INC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
+          <t>https://www.indeed.com/viewjob?jk=a35bc9c9058b4a38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Snowflake Developer – Python &amp; SQL Server</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Unitedone health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
+          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
+          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Mongo DB</t>
+          <t>Senior Data Engineer with Data Analytics</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Kanan solutions</t>
+          <t>U.S. Bank</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hopkins, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,59 +1266,59 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
+          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Development - Cloud Platform</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Oak Brook, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, ECS, Azure, Scala, Kafka, Splunk, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-15</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=999c2fd6b4078473</t>
+          <t>https://www.indeed.com/viewjob?jk=e622b2e76eb112c1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lynden</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>SeaTac, WA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,42 +1326,42 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
+          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,977 +1371,977 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
+          <t>https://www.indeed.com/viewjob?jk=403061dcf440ec37</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=99f4a1c92a28581b</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=534a121db23077a6</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=845609474cda1ceb</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=7bac106108d2cb48</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=895ccfdfabd80a00</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=60845048c5e70011</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=36e72d3d377212ef</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
+          <t>https://www.indeed.com/viewjob?jk=067a57b264a3d769</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>TrueScripts Management Services</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Washington, IN, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+          <t>https://www.indeed.com/viewjob?jk=11c98ecd4628c5e9</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=a65c027dc2ff5a07</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=bf8e8d6efc4e8fd0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=1e49d76b2d69dfa2</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Analytics Engineer I</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+          <t>https://www.indeed.com/viewjob?jk=134d9282cf37a0ae</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Azure IoT Solutions Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Bio-Tech Lab Services, LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>RDS, Azure, Event Hubs, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, AKS, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cfe7343b152cfe6</t>
+          <t>https://www.indeed.com/viewjob?jk=e72c66f56235b87a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Enterprise Architect</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Native American Industrial Solutions, LLC (NAIS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
+          <t>https://www.indeed.com/viewjob?jk=331da26c68435ffe</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74896e076c7ddf35</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85728be0a6515e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=dd873054d15e8766</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, Azure, Databricks, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02e08592b97e0e85</t>
+          <t>https://www.indeed.com/viewjob?jk=6d86099ef8b381b8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Wright-Patterson AFB, OH, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
+          <t>https://www.indeed.com/viewjob?jk=f109e5071a47922c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b6cd4f20194f69</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=2649e457ca6d1f62</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=4c47e7783b37bb7f</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea03bac31fda055</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Consultant - M365 Search &amp; AI Solutions</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f1e7ff8ca49335e</t>
+          <t>https://www.indeed.com/viewjob?jk=265ad9188f08d4fa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Scientist, Development</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc2bbb946ec5705</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Quality Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Insperity</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Kingwood, TX, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, Hadoop, Scala, Snowflake, Talend, dbt, Tableau, pytest</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4431a326a86a449</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9a888ebe473e5f</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer- Greater Tampa</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,522 +2351,522 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=9872e02a1d0b5a55</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a365d685f25643</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=7163db582e33e63f</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=f4818ff983fe32be</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=44025b0cc02106d4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
+          <t>https://www.indeed.com/viewjob?jk=9b9169947786f5a4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Sr Database Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd582173f03bef9</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbbee3255a67262</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=a000d31ba2da0950</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bcf73c00809dc6b</t>
+          <t>https://www.indeed.com/viewjob?jk=3eea0a491e9b49dd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Application Security Engineer IV</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Edward Jones</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tempe, AZ, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>13.2</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98987962708a5fc1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d0c7c3216eba93</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Quality and Governance</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5baa7bc18a6821</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
+          <t>https://www.indeed.com/viewjob?jk=06b7ce759b03fc0a</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe68e26b4040f5d</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf7a108004d0304</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=48e2290ee4c4e6e9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,67 +2876,67 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b25498d222f29589</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr Engineer - MLOps Platform</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
+          <t>https://www.indeed.com/viewjob?jk=fe51a9b954fbdf0e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Contract Full-Stack Developer - existing application completion &amp; deployment</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>NICA</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>North Falmouth, MA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,172 +2946,172 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1624bcb33518b242</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1098dd2acf48ae</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Central One Federal Credit Union</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Shrewsbury, MA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Oracle, Data Modeling, Power BI, CI/CD, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2690489cc69e3db5</t>
+          <t>https://www.indeed.com/viewjob?jk=d2934000541a09da</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9018daddfd9b2f20</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Associate Solutions Architect</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>540</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+          <t>https://www.indeed.com/viewjob?jk=e290adebae65f2ae</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=8556b0757d0f99dc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Modeler - Mongo DB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kanan solutions</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,110 +3121,1720 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Lynden</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Schaumburg, IL, US USA</t>
+          <t>SeaTac, WA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Technical Product Owner, Data and Payment Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Princess</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fort Lauderdale, FL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Snowflake, Oracle, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=27b94e7f6f2a8337</t>
+          <t>https://www.indeed.com/viewjob?jk=7211706c4fa77eff</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Mastercard</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Hadoop, HDFS, Hive, Spark, Scala, Kafka, ELT, MLOps</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>CNH Industrial</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Sioux Falls, SD, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Kind Lending</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Database Administrator</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>RELI Group Inc</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Hunter Industries</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>San Marcos, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer - Azure</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CCC Intelligent Solutions</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Whisker</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>West Chester, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>West Chester, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, ETL, Python</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ad4a5d391e5cb08</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>TrueScripts Management Services</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Washington, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>King of Prussia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Palomar Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>La Jolla, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Palomar Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Edina, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Analytics Engineer I</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Imperial PFS</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Quantum Sky</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Wright-Patterson AFB, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Senior Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Native American Industrial Solutions, LLC (NAIS)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Security Benefit</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Topeka, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Security Benefit</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Coraopolis, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Delinea</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Data Scientist, Development</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Citrin Cooperman Advisors LLC</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Data Engineer- Greater Tampa</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>MAXhealth</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Copy of Software Engineer II, Data Platform</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>American Bureau of Shipping (ABS)</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Knoxville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Data Platform Engineer (GCP)</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Innodata</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Ridgefield Park, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Data Engineer II</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>DailyPay Inc</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Sr Database Engineer</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Cox Automotive</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Draper, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, Terraform</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0fd582173f03bef9</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Marcus &amp; Millichap</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Woongjin, Inc</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Data Quality and Governance</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>HCA Healthcare</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Data Engineer - Sr. Consultant level</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Rippling</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Data Engineer - North America Fabric Care</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Procter &amp; Gamble</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Data Engineer - Sr. Consultant level</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Alliance Health Plan</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Contract Full-Stack Developer - existing application completion &amp; deployment</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>NICA</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>North Falmouth, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1624bcb33518b242</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Sr Engineer - MLOps Platform</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Eden Prairie, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Associate Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>X Development</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Mountain View, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Optum</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Schaumburg, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
           <t>Ab Initio Developer</t>
         </is>
       </c>
-      <c r="B80" t="inlineStr">
+      <c r="B126" t="inlineStr">
         <is>
           <t>Key2Source INC</t>
         </is>
       </c>
-      <c r="C80" t="inlineStr">
+      <c r="C126" t="inlineStr">
         <is>
           <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
-      <c r="D80" t="n">
+      <c r="D126" t="n">
         <v>10.4</v>
       </c>
-      <c r="E80" t="inlineStr">
+      <c r="E126" t="inlineStr">
         <is>
           <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G126"/>
+  <dimension ref="A1:G117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,69 +591,69 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
+          <t>https://www.indeed.com/viewjob?jk=93c578df954821f2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Veridic Solutions</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Synapse Analytics, BigQuery, Scala, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dc73ec2502e27a3</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Veridic Solutions</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,42 +661,42 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, Redshift, Azure, Synapse Analytics, BigQuery, Scala, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=5dc73ec2502e27a3</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>senior Data Engineer</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5061b072e1bbd6</t>
+          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Westbrook Partners</t>
+          <t>Waystar</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=5b5061b072e1bbd6</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Westbrook Partners</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
+          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Product Owner - Cloud Contact Center (CCaaS) &amp; Data Platform</t>
+          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, SQS, SNS, IAM, RDS, Azure, Data Factory</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ea14ffde25c4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - AI</t>
+          <t>Product Owner - Cloud Contact Center (CCaaS) &amp; Data Platform</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dairy Farmers of America, Inc.</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, SQS, SNS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
+          <t>https://www.indeed.com/viewjob?jk=83ea14ffde25c4ae</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
+          <t>Sr. Data Engineer - AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>Dairy Farmers of America, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
+          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
         </is>
       </c>
     </row>
@@ -923,52 +923,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer IV (6281)</t>
+          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>itD Tech</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, BigQuery, Hive, Spark, Scala, Spark Streaming, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2638fbb6172c3dae</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior SAP Sales and Service Cloud Consultant</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Data Solutions LLC</t>
+          <t>JACK Entertainment</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
+          <t>https://www.indeed.com/viewjob?jk=ddeffbcda3a30081</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Palantir Data engineer - Forward Deployment Engineers</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AI SPINS INC</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35bc9c9058b4a38</t>
+          <t>https://www.indeed.com/viewjob?jk=abd794d42375295b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior SAP Sales and Service Cloud Consultant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Data Solutions LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Snowflake Developer – Python &amp; SQL Server</t>
+          <t>Palantir Data engineer - Forward Deployment Engineers</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unitedone health</t>
+          <t>AI SPINS INC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,34 +1081,34 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
+          <t>https://www.indeed.com/viewjob?jk=a35bc9c9058b4a38</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
+          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
+          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Snowflake Developer – Python &amp; SQL Server</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Unitedone health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08766dbd36ab8fcd</t>
+          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>Emed</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ff0ddbadc99534</t>
+          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c17d7842b363140</t>
+          <t>https://www.indeed.com/viewjob?jk=e622b2e76eb112c1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer with Data Analytics</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Hopkins, MN, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Scala, SQL Server, Data Modeling, Dimensional Modeling, Star Schema</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=98744b5e8a4fd0c0</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1283,15 +1283,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e622b2e76eb112c1</t>
+          <t>https://www.indeed.com/viewjob?jk=403061dcf440ec37</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AI/ML Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,34 +1326,34 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Hadoop, Spark, PySpark, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f127a479735d551c</t>
+          <t>https://www.indeed.com/viewjob?jk=99f4a1c92a28581b</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=534a121db23077a6</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403061dcf440ec37</t>
+          <t>https://www.indeed.com/viewjob?jk=845609474cda1ceb</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f4a1c92a28581b</t>
+          <t>https://www.indeed.com/viewjob?jk=7bac106108d2cb48</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=534a121db23077a6</t>
+          <t>https://www.indeed.com/viewjob?jk=895ccfdfabd80a00</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845609474cda1ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=60845048c5e70011</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bac106108d2cb48</t>
+          <t>https://www.indeed.com/viewjob?jk=36e72d3d377212ef</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895ccfdfabd80a00</t>
+          <t>https://www.indeed.com/viewjob?jk=067a57b264a3d769</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60845048c5e70011</t>
+          <t>https://www.indeed.com/viewjob?jk=11c98ecd4628c5e9</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e72d3d377212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=a65c027dc2ff5a07</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067a57b264a3d769</t>
+          <t>https://www.indeed.com/viewjob?jk=bf8e8d6efc4e8fd0</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c98ecd4628c5e9</t>
+          <t>https://www.indeed.com/viewjob?jk=1e49d76b2d69dfa2</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65c027dc2ff5a07</t>
+          <t>https://www.indeed.com/viewjob?jk=134d9282cf37a0ae</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf8e8d6efc4e8fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=e72c66f56235b87a</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e49d76b2d69dfa2</t>
+          <t>https://www.indeed.com/viewjob?jk=331da26c68435ffe</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=134d9282cf37a0ae</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85728be0a6515e</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72c66f56235b87a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd873054d15e8766</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=331da26c68435ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=6d86099ef8b381b8</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85728be0a6515e</t>
+          <t>https://www.indeed.com/viewjob?jk=f109e5071a47922c</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd873054d15e8766</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b6cd4f20194f69</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d86099ef8b381b8</t>
+          <t>https://www.indeed.com/viewjob?jk=2649e457ca6d1f62</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f109e5071a47922c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c47e7783b37bb7f</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b6cd4f20194f69</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea03bac31fda055</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649e457ca6d1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=265ad9188f08d4fa</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c47e7783b37bb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc2bbb946ec5705</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea03bac31fda055</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9a888ebe473e5f</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265ad9188f08d4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=9872e02a1d0b5a55</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc2bbb946ec5705</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a365d685f25643</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9a888ebe473e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=7163db582e33e63f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9872e02a1d0b5a55</t>
+          <t>https://www.indeed.com/viewjob?jk=f4818ff983fe32be</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a365d685f25643</t>
+          <t>https://www.indeed.com/viewjob?jk=44025b0cc02106d4</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7163db582e33e63f</t>
+          <t>https://www.indeed.com/viewjob?jk=9b9169947786f5a4</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4818ff983fe32be</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbbee3255a67262</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44025b0cc02106d4</t>
+          <t>https://www.indeed.com/viewjob?jk=a000d31ba2da0950</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b9169947786f5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=3eea0a491e9b49dd</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbbee3255a67262</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d0c7c3216eba93</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a000d31ba2da0950</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5baa7bc18a6821</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eea0a491e9b49dd</t>
+          <t>https://www.indeed.com/viewjob?jk=06b7ce759b03fc0a</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d0c7c3216eba93</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe68e26b4040f5d</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5baa7bc18a6821</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf7a108004d0304</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b7ce759b03fc0a</t>
+          <t>https://www.indeed.com/viewjob?jk=48e2290ee4c4e6e9</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe68e26b4040f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=b25498d222f29589</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf7a108004d0304</t>
+          <t>https://www.indeed.com/viewjob?jk=fe51a9b954fbdf0e</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e2290ee4c4e6e9</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1098dd2acf48ae</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b25498d222f29589</t>
+          <t>https://www.indeed.com/viewjob?jk=d2934000541a09da</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe51a9b954fbdf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9018daddfd9b2f20</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1098dd2acf48ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e290adebae65f2ae</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2934000541a09da</t>
+          <t>https://www.indeed.com/viewjob?jk=8556b0757d0f99dc</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Senior Data Modeler - Mongo DB</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Kanan solutions</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9018daddfd9b2f20</t>
+          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Lynden</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>SeaTac, WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,14 +3051,14 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e290adebae65f2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3068,15 +3068,15 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556b0757d0f99dc</t>
+          <t>https://www.indeed.com/viewjob?jk=7211706c4fa77eff</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Mongo DB</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kanan solutions</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Databricks, Hadoop, HDFS, Hive, Spark, Scala, Kafka, ELT, MLOps</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,59 +3121,59 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lynden</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>SeaTac, WA, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7211706c4fa77eff</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Hunter Industries</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Marcos, CA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Hive, Spark, Scala, Kafka, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
+          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Engineer - Azure</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>CCC Intelligent Solutions</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Kind Lending</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Medallion Architecture, BigQuery, Scala, Snowflake, Data Modeling, Dimensional Modeling, Star Schema, Dimension Tables</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=243ccfa38c1e88ca</t>
+          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, ETL, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=802bfdff019309e4</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad4a5d391e5cb08</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>TrueScripts Management Services</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, IN, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Analytics Engineer I</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,34 +3601,34 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, ETL, Python</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad4a5d391e5cb08</t>
+          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Enterprise Architect</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>TrueScripts Management Services</t>
+          <t>Native American Industrial Solutions, LLC (NAIS)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Washington, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Wright-Patterson AFB, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Analytics Engineer I</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Wright-Patterson AFB, OH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Enterprise Architect</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Native American Industrial Solutions, LLC (NAIS)</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Scientist, Development</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,67 +3891,67 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer- Greater Tampa</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,19 +4031,19 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Scientist, Development</t>
+          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Marcus &amp; Millichap</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Data Engineer- Greater Tampa</t>
+          <t>Sr Database Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,42 +4091,42 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, Terraform</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd582173f03bef9</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Senior Data Engineer - Data Quality and Governance</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, Snowflake, ETL, dbt, Tableau</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93fadb888f0de602</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr Database Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,94 +4276,94 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd582173f03bef9</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>Pacific Consulting</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Salem, VA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
+          <t>https://www.indeed.com/viewjob?jk=0e8bd5938a7b9489</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Backend Engineer _ AI Gateway- Bilingual (Korean/ English)</t>
+          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Woongjin, Inc</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>IAM, Azure, Kafka, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1f5be991165eeea</t>
+          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Quality and Governance</t>
+          <t>Sr Engineer - MLOps Platform</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
+          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Contract Full-Stack Developer - existing application completion &amp; deployment</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NICA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>North Falmouth, MA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
+          <t>https://www.indeed.com/viewjob?jk=1624bcb33518b242</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>X Development</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Ab Initio Developer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Key2Source INC</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4520,321 +4520,6 @@
         </is>
       </c>
       <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Alliance Health Plan</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>Morrisville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Contract Full-Stack Developer - existing application completion &amp; deployment</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>NICA</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>North Falmouth, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1624bcb33518b242</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Sr Engineer - MLOps Platform</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Target</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Brooklyn Park, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, ETL, dbt, Power BI</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4ae2b9e8142c83db</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Associate Solutions Architect</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Arlington, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Oracle, Data Modeling, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1192db5e6cd9fd1</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>X Development</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Schaumburg, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Splunk, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8ebced2ce7455ee</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Ab Initio Developer</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Key2Source INC</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -818,25 +818,25 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Product Owner - Cloud Contact Center (CCaaS) &amp; Data Platform</t>
+          <t>Sr. Data Engineer - AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Betsol</t>
+          <t>Dairy Farmers of America, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Broomfield, CO, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, SQS, SNS, IAM, RDS, Azure, Data Factory</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83ea14ffde25c4ae</t>
+          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - AI</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dairy Farmers of America, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Scala, Oracle, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
+          <t>https://www.indeed.com/viewjob?jk=da5d92ba9e6d3e13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Scala, Oracle, MySQL, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5d92ba9e6d3e13</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>JACK Entertainment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
+          <t>https://www.indeed.com/viewjob?jk=ddeffbcda3a30081</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JACK Entertainment</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddeffbcda3a30081</t>
+          <t>https://www.indeed.com/viewjob?jk=abd794d42375295b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior SAP Sales and Service Cloud Consultant</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Data Solutions LLC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd794d42375295b</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior SAP Sales and Service Cloud Consultant</t>
+          <t>Palantir Data engineer - Forward Deployment Engineers</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Data Solutions LLC</t>
+          <t>AI SPINS INC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
+          <t>https://www.indeed.com/viewjob?jk=a35bc9c9058b4a38</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Palantir Data engineer - Forward Deployment Engineers</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AI SPINS INC</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery</t>
+          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35bc9c9058b4a38</t>
+          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Snowflake Developer – Python &amp; SQL Server</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Unitedone health</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
+          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
+          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Snowflake Developer – Python &amp; SQL Server</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Unitedone health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,34 +1151,34 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
+          <t>https://www.indeed.com/viewjob?jk=695b8a15f31b95e9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Emed</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, IAM, RDS, BigQuery, Snowflake, Data Modeling, Star Schema, dbt, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d9b36986b012526</t>
+          <t>https://www.indeed.com/viewjob?jk=0d45121b0e1810c1</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,59 +1231,59 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e622b2e76eb112c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f609822c97459ef7</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=e622b2e76eb112c1</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403061dcf440ec37</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Technology Specialist II - Data Architect - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f4a1c92a28581b</t>
+          <t>https://www.indeed.com/viewjob?jk=31ca165a02301fbf</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=534a121db23077a6</t>
+          <t>https://www.indeed.com/viewjob?jk=403061dcf440ec37</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845609474cda1ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=99f4a1c92a28581b</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bac106108d2cb48</t>
+          <t>https://www.indeed.com/viewjob?jk=534a121db23077a6</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895ccfdfabd80a00</t>
+          <t>https://www.indeed.com/viewjob?jk=845609474cda1ceb</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60845048c5e70011</t>
+          <t>https://www.indeed.com/viewjob?jk=7bac106108d2cb48</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e72d3d377212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=895ccfdfabd80a00</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067a57b264a3d769</t>
+          <t>https://www.indeed.com/viewjob?jk=60845048c5e70011</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c98ecd4628c5e9</t>
+          <t>https://www.indeed.com/viewjob?jk=36e72d3d377212ef</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65c027dc2ff5a07</t>
+          <t>https://www.indeed.com/viewjob?jk=067a57b264a3d769</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf8e8d6efc4e8fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=11c98ecd4628c5e9</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e49d76b2d69dfa2</t>
+          <t>https://www.indeed.com/viewjob?jk=a65c027dc2ff5a07</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=134d9282cf37a0ae</t>
+          <t>https://www.indeed.com/viewjob?jk=bf8e8d6efc4e8fd0</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72c66f56235b87a</t>
+          <t>https://www.indeed.com/viewjob?jk=1e49d76b2d69dfa2</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=331da26c68435ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=134d9282cf37a0ae</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85728be0a6515e</t>
+          <t>https://www.indeed.com/viewjob?jk=e72c66f56235b87a</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd873054d15e8766</t>
+          <t>https://www.indeed.com/viewjob?jk=331da26c68435ffe</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d86099ef8b381b8</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85728be0a6515e</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f109e5071a47922c</t>
+          <t>https://www.indeed.com/viewjob?jk=dd873054d15e8766</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b6cd4f20194f69</t>
+          <t>https://www.indeed.com/viewjob?jk=6d86099ef8b381b8</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649e457ca6d1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=f109e5071a47922c</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c47e7783b37bb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b6cd4f20194f69</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea03bac31fda055</t>
+          <t>https://www.indeed.com/viewjob?jk=2649e457ca6d1f62</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265ad9188f08d4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=4c47e7783b37bb7f</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc2bbb946ec5705</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea03bac31fda055</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9a888ebe473e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=265ad9188f08d4fa</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9872e02a1d0b5a55</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc2bbb946ec5705</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a365d685f25643</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9a888ebe473e5f</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7163db582e33e63f</t>
+          <t>https://www.indeed.com/viewjob?jk=9872e02a1d0b5a55</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4818ff983fe32be</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a365d685f25643</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44025b0cc02106d4</t>
+          <t>https://www.indeed.com/viewjob?jk=7163db582e33e63f</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b9169947786f5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=f4818ff983fe32be</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbbee3255a67262</t>
+          <t>https://www.indeed.com/viewjob?jk=44025b0cc02106d4</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a000d31ba2da0950</t>
+          <t>https://www.indeed.com/viewjob?jk=9b9169947786f5a4</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eea0a491e9b49dd</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbbee3255a67262</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d0c7c3216eba93</t>
+          <t>https://www.indeed.com/viewjob?jk=a000d31ba2da0950</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5baa7bc18a6821</t>
+          <t>https://www.indeed.com/viewjob?jk=3eea0a491e9b49dd</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b7ce759b03fc0a</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d0c7c3216eba93</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe68e26b4040f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5baa7bc18a6821</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf7a108004d0304</t>
+          <t>https://www.indeed.com/viewjob?jk=06b7ce759b03fc0a</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e2290ee4c4e6e9</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe68e26b4040f5d</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b25498d222f29589</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf7a108004d0304</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe51a9b954fbdf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=48e2290ee4c4e6e9</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1098dd2acf48ae</t>
+          <t>https://www.indeed.com/viewjob?jk=b25498d222f29589</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2934000541a09da</t>
+          <t>https://www.indeed.com/viewjob?jk=fe51a9b954fbdf0e</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9018daddfd9b2f20</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1098dd2acf48ae</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e290adebae65f2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=d2934000541a09da</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556b0757d0f99dc</t>
+          <t>https://www.indeed.com/viewjob?jk=9018daddfd9b2f20</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Mongo DB</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kanan solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
+          <t>https://www.indeed.com/viewjob?jk=e290adebae65f2ae</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Lynden</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>SeaTac, WA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
+          <t>https://www.indeed.com/viewjob?jk=8556b0757d0f99dc</t>
         </is>
       </c>
     </row>
@@ -3063,20 +3063,20 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Lynden</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>SeaTac, WA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7211706c4fa77eff</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Modeler - Mongo DB</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Kanan solutions</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Hive, Spark, Scala, Kafka, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
+          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=7211706c4fa77eff</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Databricks, Hadoop, HDFS, Hive, Spark, Scala, Kafka, ELT, MLOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Hunter Industries</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>San Marcos, CA, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Snowflake, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=987cd62585084d2b</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer - Azure</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CCC Intelligent Solutions</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60123f1a31b96503</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
@@ -3688,17 +3688,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
@@ -3793,17 +3793,17 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data Scientist, Development</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Bed Bath &amp; Beyond</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>Google Cloud Platform, Hadoop, HBase, Spark, Scala, Kafka, Cassandra, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=4e18063e9579ba86</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Engineer- Greater Tampa</t>
+          <t>Data Scientist, Development</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,34 +3916,34 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Data Engineer- Greater Tampa</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,34 +3951,34 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>American Bureau of Shipping (ABS)</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Knoxville, TN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
+          <t>Data Platform Engineer (GCP)</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>Innodata</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ridgefield Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
+          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr Database Engineer</t>
+          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Marcus &amp; Millichap</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,7 +4091,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, Terraform</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd582173f03bef9</t>
+          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Quality and Governance</t>
+          <t>Sr Database Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, Terraform</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,59 +4136,59 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd582173f03bef9</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Software Engineer II (Backend, Platform)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Whoop</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
+          <t>https://www.indeed.com/viewjob?jk=145abebc67be2858</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Senior Data Engineer - Data Quality and Governance</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>CLAIR</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,17 +4231,17 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=62b06149f1d5d261</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Pacific Consulting</t>
+          <t>Rippling</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Salem, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, SQL</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e8bd5938a7b9489</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
+          <t>Data Engineer - North America Fabric Care</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>Procter &amp; Gamble</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr Engineer - MLOps Platform</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, GCP, Vertex AI, Scala, NoSQL, MLOps, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=83adac9442c00b06</t>
+          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Contract Full-Stack Developer - existing application completion &amp; deployment</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NICA</t>
+          <t>Pacific Consulting</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>North Falmouth, MA, US USA</t>
+          <t>Salem, VA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, MySQL, CI/CD, Jenkins, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1624bcb33518b242</t>
+          <t>https://www.indeed.com/viewjob?jk=0e8bd5938a7b9489</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,34 +4441,34 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineering, Machine Learning Operations, Tapestry</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>X Development</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, BigQuery, Vertex AI, Scala, MLOps, CI/CD, GitHub Actions, Terraform</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ded9a77a1d06a7bc</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G117"/>
+  <dimension ref="A1:G124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,52 +538,52 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
+          <t>Software Engineer V, AI Digital &amp; Engineering Software</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>X-Energy</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>19.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
+          <t>https://www.indeed.com/viewjob?jk=3a922959a62dc33f</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>National Information Solutions Cooperative (NISC)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c578df954821f2</t>
+          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,42 +626,42 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
+          <t>https://www.indeed.com/viewjob?jk=93c578df954821f2</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III, AI Digital &amp; Engineering Software</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Veridic Solutions</t>
+          <t>X-Energy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Synapse Analytics, BigQuery, Scala, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dc73ec2502e27a3</t>
+          <t>https://www.indeed.com/viewjob?jk=724dd35cc9ba9c68</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>senior Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Waystar</t>
+          <t>Veridic Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Medallion Architecture, Google Cloud Platform, GCP, BigQuery, Scala, Snowflake</t>
+          <t>AWS, Redshift, Azure, Synapse Analytics, BigQuery, Scala, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b5061b072e1bbd6</t>
+          <t>https://www.indeed.com/viewjob?jk=5dc73ec2502e27a3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Westbrook Partners</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Westbrook Partners</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
+          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - AI</t>
+          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dairy Farmers of America, Inc.</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Sr. Data Engineer - AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Dairy Farmers of America, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Scala, Oracle, MySQL, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5d92ba9e6d3e13</t>
+          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,69 +906,69 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Scala, Oracle, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
+          <t>https://www.indeed.com/viewjob?jk=da5d92ba9e6d3e13</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JACK Entertainment</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddeffbcda3a30081</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>JACK Entertainment</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd794d42375295b</t>
+          <t>https://www.indeed.com/viewjob?jk=ddeffbcda3a30081</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior SAP Sales and Service Cloud Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Data Solutions LLC</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,19 +1021,19 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
+          <t>https://www.indeed.com/viewjob?jk=abd794d42375295b</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Palantir Data engineer - Forward Deployment Engineers</t>
+          <t>Senior SAP Sales and Service Cloud Consultant</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AI SPINS INC</t>
+          <t>Data Solutions LLC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1042,11 +1042,11 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35bc9c9058b4a38</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Palantir Data engineer - Forward Deployment Engineers</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>AI SPINS INC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
+          <t>https://www.indeed.com/viewjob?jk=a35bc9c9058b4a38</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Snowflake Developer – Python &amp; SQL Server</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unitedone health</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,34 +1116,34 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Snowflake, Time Travel, SQL Server, Star Schema, Dimension Tables, ETL, ELT</t>
+          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d501f7eec5c487a</t>
+          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=695b8a15f31b95e9</t>
+          <t>https://www.indeed.com/viewjob?jk=e622b2e76eb112c1</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d45121b0e1810c1</t>
+          <t>https://www.indeed.com/viewjob?jk=695b8a15f31b95e9</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f609822c97459ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=0d45121b0e1810c1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,67 +1266,67 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e622b2e76eb112c1</t>
+          <t>https://www.indeed.com/viewjob?jk=f609822c97459ef7</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=3500a77261ebbb93</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Technology Specialist II - Data Architect - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ca165a02301fbf</t>
+          <t>https://www.indeed.com/viewjob?jk=5a07575a9e0364be</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403061dcf440ec37</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f4a1c92a28581b</t>
+          <t>https://www.indeed.com/viewjob?jk=403061dcf440ec37</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=534a121db23077a6</t>
+          <t>https://www.indeed.com/viewjob?jk=99f4a1c92a28581b</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845609474cda1ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=534a121db23077a6</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bac106108d2cb48</t>
+          <t>https://www.indeed.com/viewjob?jk=845609474cda1ceb</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895ccfdfabd80a00</t>
+          <t>https://www.indeed.com/viewjob?jk=7bac106108d2cb48</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60845048c5e70011</t>
+          <t>https://www.indeed.com/viewjob?jk=895ccfdfabd80a00</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e72d3d377212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=60845048c5e70011</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067a57b264a3d769</t>
+          <t>https://www.indeed.com/viewjob?jk=36e72d3d377212ef</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c98ecd4628c5e9</t>
+          <t>https://www.indeed.com/viewjob?jk=067a57b264a3d769</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65c027dc2ff5a07</t>
+          <t>https://www.indeed.com/viewjob?jk=11c98ecd4628c5e9</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf8e8d6efc4e8fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=a65c027dc2ff5a07</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e49d76b2d69dfa2</t>
+          <t>https://www.indeed.com/viewjob?jk=bf8e8d6efc4e8fd0</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=134d9282cf37a0ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1e49d76b2d69dfa2</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72c66f56235b87a</t>
+          <t>https://www.indeed.com/viewjob?jk=134d9282cf37a0ae</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=331da26c68435ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=e72c66f56235b87a</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85728be0a6515e</t>
+          <t>https://www.indeed.com/viewjob?jk=331da26c68435ffe</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd873054d15e8766</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85728be0a6515e</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d86099ef8b381b8</t>
+          <t>https://www.indeed.com/viewjob?jk=dd873054d15e8766</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f109e5071a47922c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d86099ef8b381b8</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b6cd4f20194f69</t>
+          <t>https://www.indeed.com/viewjob?jk=f109e5071a47922c</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649e457ca6d1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b6cd4f20194f69</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c47e7783b37bb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=2649e457ca6d1f62</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea03bac31fda055</t>
+          <t>https://www.indeed.com/viewjob?jk=4c47e7783b37bb7f</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265ad9188f08d4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea03bac31fda055</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc2bbb946ec5705</t>
+          <t>https://www.indeed.com/viewjob?jk=265ad9188f08d4fa</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9a888ebe473e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc2bbb946ec5705</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9872e02a1d0b5a55</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9a888ebe473e5f</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a365d685f25643</t>
+          <t>https://www.indeed.com/viewjob?jk=9872e02a1d0b5a55</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7163db582e33e63f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a365d685f25643</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4818ff983fe32be</t>
+          <t>https://www.indeed.com/viewjob?jk=7163db582e33e63f</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44025b0cc02106d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f4818ff983fe32be</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b9169947786f5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=44025b0cc02106d4</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbbee3255a67262</t>
+          <t>https://www.indeed.com/viewjob?jk=9b9169947786f5a4</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a000d31ba2da0950</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbbee3255a67262</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eea0a491e9b49dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a000d31ba2da0950</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d0c7c3216eba93</t>
+          <t>https://www.indeed.com/viewjob?jk=3eea0a491e9b49dd</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5baa7bc18a6821</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d0c7c3216eba93</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b7ce759b03fc0a</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5baa7bc18a6821</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe68e26b4040f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=06b7ce759b03fc0a</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf7a108004d0304</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe68e26b4040f5d</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e2290ee4c4e6e9</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf7a108004d0304</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b25498d222f29589</t>
+          <t>https://www.indeed.com/viewjob?jk=48e2290ee4c4e6e9</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe51a9b954fbdf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b25498d222f29589</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1098dd2acf48ae</t>
+          <t>https://www.indeed.com/viewjob?jk=fe51a9b954fbdf0e</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2934000541a09da</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1098dd2acf48ae</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9018daddfd9b2f20</t>
+          <t>https://www.indeed.com/viewjob?jk=d2934000541a09da</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e290adebae65f2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9018daddfd9b2f20</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556b0757d0f99dc</t>
+          <t>https://www.indeed.com/viewjob?jk=e290adebae65f2ae</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lynden</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>SeaTac, WA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
+          <t>https://www.indeed.com/viewjob?jk=8556b0757d0f99dc</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Mongo DB</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kanan solutions</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,42 +3111,42 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1f698284725984</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,124 +3156,124 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7211706c4fa77eff</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb838c30917dc45</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Hive, Spark, Scala, Kafka, ELT, MLOps</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
+          <t>https://www.indeed.com/viewjob?jk=e506811c0b2cc445</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=18381d7ceeaba33a</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc2deee2a3e4d7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Technology Specialist II - Data Architect - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -3282,81 +3282,81 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=31ca165a02301fbf</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>Lynden</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>SeaTac, WA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
+          <t>Senior Data Modeler - Mongo DB</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Kanan solutions</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
         </is>
       </c>
     </row>
@@ -3378,90 +3378,90 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
+          <t>https://www.indeed.com/viewjob?jk=7211706c4fa77eff</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, ETL, Python</t>
+          <t>AWS, Databricks, Hadoop, HDFS, Hive, Spark, Scala, Kafka, ELT, MLOps</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad4a5d391e5cb08</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TrueScripts Management Services</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Washington, IN, US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Analytics Engineer I</t>
+          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Enterprise Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Native American Industrial Solutions, LLC (NAIS)</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Wright-Patterson AFB, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
+          <t>https://www.indeed.com/viewjob?jk=85cd0d74b3f6d1fd</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,34 +3706,34 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=06a5cdb578318149</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,34 +3741,34 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, ETL, Python</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad4a5d391e5cb08</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TrueScripts Management Services</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Washington, IN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,67 +3856,67 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Bed Bath &amp; Beyond</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Hadoop, HBase, Spark, Scala, Kafka, Cassandra, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e18063e9579ba86</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data Scientist, Development</t>
+          <t>Analytics Engineer I</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>Imperial PFS</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,67 +3926,67 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Data Engineer- Greater Tampa</t>
+          <t>Senior Enterprise Architect</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Native American Industrial Solutions, LLC (NAIS)</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Wright-Patterson AFB, OH, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>American Bureau of Shipping (ABS)</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Knoxville, TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Databricks, Spark, Scala, Snowflake, ETL, ELT, Docker</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c49b3214cf3972d</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Data Platform Engineer (GCP)</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Innodata</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Ridgefield Park, NJ, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>IAM, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Scala, CI/CD, Terraform</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65208b050c6c3d05</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Oracle Cloud Fusion Technical Data Architect and Reporting Analyst (Contract)</t>
+          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Marcus &amp; Millichap</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Coraopolis, PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, Dimensional Modeling, Star Schema, Fact Tables, ETL, Power BI</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9036892ad365fcc3</t>
+          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr Database Engineer</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Topeka, KS, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, Terraform</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,172 +4136,172 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd582173f03bef9</t>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend, Platform)</t>
+          <t>Senior Data Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Whoop</t>
+          <t>Security Benefit</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Docker</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=145abebc67be2858</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Quality and Governance</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Bed Bath &amp; Beyond</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
+          <t>Google Cloud Platform, Hadoop, HBase, Spark, Scala, Kafka, Cassandra, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
+          <t>https://www.indeed.com/viewjob?jk=4e18063e9579ba86</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Scientist, Development</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>CLAIR</t>
+          <t>Citrin Cooperman Advisors LLC</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62b06149f1d5d261</t>
+          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer- Greater Tampa</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
+          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Sr Database Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Cox Automotive</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Draper, UT, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Kinesis, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, Terraform</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,59 +4346,59 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=0fd582173f03bef9</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Software Engineer II (Backend, Platform)</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Whoop</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=583ac829a05c951b</t>
+          <t>https://www.indeed.com/viewjob?jk=145abebc67be2858</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Senior Data Engineer - Data Quality and Governance</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Pacific Consulting</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Salem, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, SQL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e8bd5938a7b9489</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Estero, FL, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
+          <t>AWS, Kinesis, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=c3cb1b92b52d7a99</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CLAIR</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=62b06149f1d5d261</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Key2Source INC</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,15 +4511,260 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Democratic National Committee</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Data Engineer - North America Fabric Care</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Procter &amp; Gamble</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Alliance Health Plan</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Systems Administrator</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Pacific Consulting</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Salem, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e8bd5938a7b9489</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>VIE - Software Engineer (based in Miami)</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Pelico</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=072180860b5c5965</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Ab Initio Developer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Key2Source INC</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Alpharetta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
           <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F124" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G124" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
         </is>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G124"/>
+  <dimension ref="A1:G177"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -643,17 +643,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer III, AI Digital &amp; Engineering Software</t>
+          <t>Senior AI Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>X-Energy</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,24 +671,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dd35cc9ba9c68</t>
+          <t>https://www.indeed.com/viewjob?jk=5c52720211e7a971</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
+          <t>Software Engineer III, AI Digital &amp; Engineering Software</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>X-Energy</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,69 +696,69 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
+          <t>https://www.indeed.com/viewjob?jk=724dd35cc9ba9c68</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Veridic Solutions</t>
+          <t>CareFirst BlueCross BlueShield</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Synapse Analytics, BigQuery, Scala, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dc73ec2502e27a3</t>
+          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Veridic Solutions</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, Redshift, Azure, Synapse Analytics, BigQuery, Scala, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=5dc73ec2502e27a3</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Westbrook Partners</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Westbrook Partners</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
+          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - AI</t>
+          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dairy Farmers of America, Inc.</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Sr. Data Engineer - AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Dairy Farmers of America, Inc.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Scala, Oracle, MySQL, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5d92ba9e6d3e13</t>
+          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,69 +941,69 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Scala, Oracle, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
+          <t>https://www.indeed.com/viewjob?jk=da5d92ba9e6d3e13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JACK Entertainment</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddeffbcda3a30081</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>JACK Entertainment</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd794d42375295b</t>
+          <t>https://www.indeed.com/viewjob?jk=ddeffbcda3a30081</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior SAP Sales and Service Cloud Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Data Solutions LLC</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
+          <t>https://www.indeed.com/viewjob?jk=abd794d42375295b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Palantir Data engineer - Forward Deployment Engineers</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>AI SPINS INC</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery</t>
+          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,19 +1091,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35bc9c9058b4a38</t>
+          <t>https://www.indeed.com/viewjob?jk=e97bf8ea06c2dcbb</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>ISOD Limited</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
+          <t>https://www.indeed.com/viewjob?jk=91f52b29094f2ea2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Senior SAP Sales and Service Cloud Consultant</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Data Solutions LLC</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e622b2e76eb112c1</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer (Microsoft Azure)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=695b8a15f31b95e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7a0b93ee4cad8277</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Palantir Data engineer - Forward Deployment Engineers</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>AI SPINS INC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d45121b0e1810c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a35bc9c9058b4a38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f609822c97459ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3500a77261ebbb93</t>
+          <t>https://www.indeed.com/viewjob?jk=695b8a15f31b95e9</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a07575a9e0364be</t>
+          <t>https://www.indeed.com/viewjob?jk=0d45121b0e1810c1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=f609822c97459ef7</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403061dcf440ec37</t>
+          <t>https://www.indeed.com/viewjob?jk=3500a77261ebbb93</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f4a1c92a28581b</t>
+          <t>https://www.indeed.com/viewjob?jk=5a07575a9e0364be</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=534a121db23077a6</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd78528f3cfeae1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,14 +1511,14 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845609474cda1ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=a03747dc8123c18e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1528,15 +1528,15 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bac106108d2cb48</t>
+          <t>https://www.indeed.com/viewjob?jk=e622b2e76eb112c1</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895ccfdfabd80a00</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60845048c5e70011</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1f698284725984</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e72d3d377212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb838c30917dc45</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067a57b264a3d769</t>
+          <t>https://www.indeed.com/viewjob?jk=e506811c0b2cc445</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c98ecd4628c5e9</t>
+          <t>https://www.indeed.com/viewjob?jk=18381d7ceeaba33a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65c027dc2ff5a07</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc2deee2a3e4d7</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Technology Specialist II - Data Architect - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf8e8d6efc4e8fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=31ca165a02301fbf</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e49d76b2d69dfa2</t>
+          <t>https://www.indeed.com/viewjob?jk=403061dcf440ec37</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=134d9282cf37a0ae</t>
+          <t>https://www.indeed.com/viewjob?jk=99f4a1c92a28581b</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72c66f56235b87a</t>
+          <t>https://www.indeed.com/viewjob?jk=534a121db23077a6</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=331da26c68435ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=845609474cda1ceb</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85728be0a6515e</t>
+          <t>https://www.indeed.com/viewjob?jk=7bac106108d2cb48</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd873054d15e8766</t>
+          <t>https://www.indeed.com/viewjob?jk=895ccfdfabd80a00</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d86099ef8b381b8</t>
+          <t>https://www.indeed.com/viewjob?jk=60845048c5e70011</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f109e5071a47922c</t>
+          <t>https://www.indeed.com/viewjob?jk=36e72d3d377212ef</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b6cd4f20194f69</t>
+          <t>https://www.indeed.com/viewjob?jk=067a57b264a3d769</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649e457ca6d1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=11c98ecd4628c5e9</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c47e7783b37bb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=a65c027dc2ff5a07</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea03bac31fda055</t>
+          <t>https://www.indeed.com/viewjob?jk=bf8e8d6efc4e8fd0</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265ad9188f08d4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=1e49d76b2d69dfa2</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc2bbb946ec5705</t>
+          <t>https://www.indeed.com/viewjob?jk=134d9282cf37a0ae</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9a888ebe473e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=e72c66f56235b87a</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9872e02a1d0b5a55</t>
+          <t>https://www.indeed.com/viewjob?jk=331da26c68435ffe</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a365d685f25643</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85728be0a6515e</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7163db582e33e63f</t>
+          <t>https://www.indeed.com/viewjob?jk=dd873054d15e8766</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4818ff983fe32be</t>
+          <t>https://www.indeed.com/viewjob?jk=6d86099ef8b381b8</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44025b0cc02106d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f109e5071a47922c</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b9169947786f5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b6cd4f20194f69</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbbee3255a67262</t>
+          <t>https://www.indeed.com/viewjob?jk=2649e457ca6d1f62</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a000d31ba2da0950</t>
+          <t>https://www.indeed.com/viewjob?jk=4c47e7783b37bb7f</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eea0a491e9b49dd</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea03bac31fda055</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d0c7c3216eba93</t>
+          <t>https://www.indeed.com/viewjob?jk=265ad9188f08d4fa</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5baa7bc18a6821</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc2bbb946ec5705</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b7ce759b03fc0a</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9a888ebe473e5f</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe68e26b4040f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=9872e02a1d0b5a55</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf7a108004d0304</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a365d685f25643</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e2290ee4c4e6e9</t>
+          <t>https://www.indeed.com/viewjob?jk=7163db582e33e63f</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b25498d222f29589</t>
+          <t>https://www.indeed.com/viewjob?jk=f4818ff983fe32be</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe51a9b954fbdf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=44025b0cc02106d4</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1098dd2acf48ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9b9169947786f5a4</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2934000541a09da</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbbee3255a67262</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9018daddfd9b2f20</t>
+          <t>https://www.indeed.com/viewjob?jk=a000d31ba2da0950</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e290adebae65f2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=3eea0a491e9b49dd</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556b0757d0f99dc</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d0c7c3216eba93</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1f698284725984</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5baa7bc18a6821</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb838c30917dc45</t>
+          <t>https://www.indeed.com/viewjob?jk=06b7ce759b03fc0a</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e506811c0b2cc445</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe68e26b4040f5d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18381d7ceeaba33a</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf7a108004d0304</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcc2deee2a3e4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=48e2290ee4c4e6e9</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Technology Specialist II - Data Architect - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ca165a02301fbf</t>
+          <t>https://www.indeed.com/viewjob?jk=b25498d222f29589</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Lynden</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SeaTac, WA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
+          <t>https://www.indeed.com/viewjob?jk=fe51a9b954fbdf0e</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Mongo DB</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Kanan solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,24 +3356,24 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1098dd2acf48ae</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3383,15 +3383,15 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,172 +3401,172 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7211706c4fa77eff</t>
+          <t>https://www.indeed.com/viewjob?jk=d2934000541a09da</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Hive, Spark, Scala, Kafka, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
+          <t>https://www.indeed.com/viewjob?jk=9018daddfd9b2f20</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=e290adebae65f2ae</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84a78da056d3cd48</t>
+          <t>https://www.indeed.com/viewjob?jk=8556b0757d0f99dc</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Lynden</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>SeaTac, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Modeler - Mongo DB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>Kanan solutions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,67 +3576,67 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=7211706c4fa77eff</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Databricks, Hadoop, HDFS, Hive, Spark, Scala, Kafka, ELT, MLOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,102 +3646,102 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>CNH Industrial</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sioux Falls, SD, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85cd0d74b3f6d1fd</t>
+          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a5cdb578318149</t>
+          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, ETL, Python</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,452 +3751,452 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad4a5d391e5cb08</t>
+          <t>https://www.indeed.com/viewjob?jk=a21ae7255e004909</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>TrueScripts Management Services</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Washington, IN, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+          <t>https://www.indeed.com/viewjob?jk=b76b7b194c7c6249</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=a6573882e75f2256</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=afbb42f1fb391e5b</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=b4774424a7c977d0</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Analytics Engineer I</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+          <t>https://www.indeed.com/viewjob?jk=00673ec98ad396b2</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Senior Enterprise Architect</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Native American Industrial Solutions, LLC (NAIS)</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
+          <t>https://www.indeed.com/viewjob?jk=0cca2406337e3f4b</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Wright-Patterson AFB, OH, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
+          <t>https://www.indeed.com/viewjob?jk=9f87b401bf307b90</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2545a3398f75f5</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=da5709f322b6de77</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Analyst, Data &amp; Analytics Engineering</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Coraopolis, PA, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Scala, Snowflake, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c73b6b96302b8ac</t>
+          <t>https://www.indeed.com/viewjob?jk=33e7e2d41c6bbc1f</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=2bbf8d425b26cb57</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8296a32cbcd5e8</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Bed Bath &amp; Beyond</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Hadoop, HBase, Spark, Scala, Kafka, Cassandra, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,67 +4206,67 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e18063e9579ba86</t>
+          <t>https://www.indeed.com/viewjob?jk=bddcc0bf9a07cf52</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Data Scientist, Development</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Citrin Cooperman Advisors LLC</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Medallion Architecture, Spark, PySpark, Power BI, MLOps, MLflow, Python</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4dae5875a25bfbc</t>
+          <t>https://www.indeed.com/viewjob?jk=87c76b5382d91ff5</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer- Greater Tampa</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,102 +4276,102 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=e2a46dfdabaf144b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=148ea1e43d8803c0</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Sr Database Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cox Automotive</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Draper, UT, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, Terraform</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0fd582173f03bef9</t>
+          <t>https://www.indeed.com/viewjob?jk=6d122abea15bffcd</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend, Platform)</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Whoop</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,67 +4381,67 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=145abebc67be2858</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb52081cc83a1d</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Quality and Governance</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
+          <t>https://www.indeed.com/viewjob?jk=6585b0f7548a110e</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Estero, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cb1b92b52d7a99</t>
+          <t>https://www.indeed.com/viewjob?jk=b6af657ad808aca0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>CLAIR</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt, Airflow</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,137 +4486,137 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62b06149f1d5d261</t>
+          <t>https://www.indeed.com/viewjob?jk=8c71c57379755325</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4b1fb8cf73679e</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Democratic National Committee</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=eef37f19b519cfb3</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=2acd943bf9f49043</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,32 +4626,32 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=b5356ec2fad3097c</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Pacific Consulting</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Salem, VA, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, SQL</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,112 +4661,1967 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e8bd5938a7b9489</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0b088c77b432bf</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
+          <t>https://www.indeed.com/viewjob?jk=502c66caf2321daa</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>VIE - Software Engineer (based in Miami)</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Pelico</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072180860b5c5965</t>
+          <t>https://www.indeed.com/viewjob?jk=a8e35eb0472f1b04</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Ab Initio Developer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Key2Source INC</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5ea808b55ddf87a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c8d2fb8ee058fcb4</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>St. Louis, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=31e2d771ef37e989</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Corrales, NM, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5701765b8810e954</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a74fc9df8466ed80</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Upper Darby, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e350cbedde8fb5c3</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=37c3d1a6e3db03ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3fb7cf0d3892b335</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Oklahoma City, OK, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2515e91820622466</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f92266e4f2da0ea</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>TN, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5834a6a46819e223</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>OH, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d766b034a172a2ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Walnut Creek, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ab132d0ecb2e269</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=163d580eae60a657</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>OR, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c8d43b4208b386a</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Baton Rouge, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58a509ab2ac2911c</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>VA, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=289f16a53bce28f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Whisker</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Auburn Hills, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>West Chester, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>West Chester, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Arrive Logistics</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4519eed0c0bcdda8</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Senior, Data Engineer</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Carrington Mortgage Services, LLC</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=85cd0d74b3f6d1fd</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Tiger Analytics</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Redshift, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=06a5cdb578318149</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>CVS Health</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, ETL, Python</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8ad4a5d391e5cb08</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>TrueScripts Management Services</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Washington, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Lockheed Martin</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>King of Prussia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Palomar Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>La Jolla, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Sr. Data Engineer</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Palomar Holdings, Inc.</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Edina, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Analytics Engineer I</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Imperial PFS</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Kansas City, MO, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Python/GenAI Solutions Architect</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Provectus</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6ddb4f1cd1354de8</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior Enterprise Architect</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Native American Industrial Solutions, LLC (NAIS)</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Quantum Sky</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Wright-Patterson AFB, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Delinea</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Redwood City, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Security Benefit</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Topeka, KS, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Senior Data Architect</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Security Benefit</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ed0d719f5bbccf0</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Salt Lake City, UT, US USA</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Data Modeling, ETL</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=69ed747f2eb90e25</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Senior Analytics Data Engineer - Homes.com</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>CoStar Group</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Arlington, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Power BI</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b80d45c896bb26ef</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer II</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Bed Bath &amp; Beyond</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>UT, US USA</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Google Cloud Platform, Hadoop, HBase, Spark, Scala, Kafka, Cassandra, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4e18063e9579ba86</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Data Engineer- Greater Tampa</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>MAXhealth</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Copy of Software Engineer II, Data Platform</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>PlayStation</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Software Engineer II (Backend, Platform)</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Whoop</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Docker</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=145abebc67be2858</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer - Data Quality and Governance</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>HCA Healthcare</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Nashville, TN, US USA</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
         <v>10.4</v>
       </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, Oracle, SQL Server, Data Modeling, ETL, CI/CD, Python</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c2853c2a6cd9e278</t>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Sr Data Engineer</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Hertz</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Estero, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>AWS, Kinesis, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c3cb1b92b52d7a99</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>CLAIR</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt, Airflow</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=62b06149f1d5d261</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Data Engineer - Sr. Consultant level</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Analytics Engineer</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Democratic National Committee</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Data Engineer - North America Fabric Care</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Procter &amp; Gamble</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Cincinnati, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Senior Payments IT Business Analyst (AI &amp; Data Focus)</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>MUFG</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e859637db4511ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Systems Administrator</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Pacific Consulting</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Salem, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e8bd5938a7b9489</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Alliance Health Plan</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>VIE - Software Engineer (based in Miami)</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Pelico</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=072180860b5c5965</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G177"/>
+  <dimension ref="A1:G173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -713,52 +713,52 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java, Microservices, MuleSoft &amp; API Development (Remote)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>CareFirst BlueCross BlueShield</t>
+          <t>Veridic Solutions</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, Oracle, PostgreSQL, MongoDB, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, Redshift, Azure, Synapse Analytics, BigQuery, Scala, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d5b52a299e98559</t>
+          <t>https://www.indeed.com/viewjob?jk=5dc73ec2502e27a3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Veridic Solutions</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,42 +766,42 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Synapse Analytics, BigQuery, Scala, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dc73ec2502e27a3</t>
+          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>BNY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer - AI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Westbrook Partners</t>
+          <t>Dairy Farmers of America, Inc.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84364c91a0970a5c</t>
+          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Scala, Oracle, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
+          <t>https://www.indeed.com/viewjob?jk=da5d92ba9e6d3e13</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - AI</t>
+          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Dairy Farmers of America, Inc.</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JACK Entertainment</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Scala, Oracle, MySQL, Cassandra</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5d92ba9e6d3e13</t>
+          <t>https://www.indeed.com/viewjob?jk=ddeffbcda3a30081</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
+          <t>https://www.indeed.com/viewjob?jk=abd794d42375295b</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>JACK Entertainment</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddeffbcda3a30081</t>
+          <t>https://www.indeed.com/viewjob?jk=e97bf8ea06c2dcbb</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>ISOD Limited</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd794d42375295b</t>
+          <t>https://www.indeed.com/viewjob?jk=91f52b29094f2ea2</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Senior SAP Sales and Service Cloud Consultant</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Data Solutions LLC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97bf8ea06c2dcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ISOD Limited</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f52b29094f2ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd78528f3cfeae1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior SAP Sales and Service Cloud Consultant</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Data Solutions LLC</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
+          <t>https://www.indeed.com/viewjob?jk=a03747dc8123c18e</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,67 +1476,67 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd78528f3cfeae1</t>
+          <t>https://www.indeed.com/viewjob?jk=e622b2e76eb112c1</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03747dc8123c18e</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e622b2e76eb112c1</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1f698284725984</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,17 +1571,17 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb838c30917dc45</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1f698284725984</t>
+          <t>https://www.indeed.com/viewjob?jk=e506811c0b2cc445</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb838c30917dc45</t>
+          <t>https://www.indeed.com/viewjob?jk=18381d7ceeaba33a</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e506811c0b2cc445</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc2deee2a3e4d7</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Technology Specialist II - Data Architect - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18381d7ceeaba33a</t>
+          <t>https://www.indeed.com/viewjob?jk=31ca165a02301fbf</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcc2deee2a3e4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=403061dcf440ec37</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Technology Specialist II - Data Architect - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ca165a02301fbf</t>
+          <t>https://www.indeed.com/viewjob?jk=99f4a1c92a28581b</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403061dcf440ec37</t>
+          <t>https://www.indeed.com/viewjob?jk=534a121db23077a6</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f4a1c92a28581b</t>
+          <t>https://www.indeed.com/viewjob?jk=845609474cda1ceb</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=534a121db23077a6</t>
+          <t>https://www.indeed.com/viewjob?jk=7bac106108d2cb48</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845609474cda1ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=895ccfdfabd80a00</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bac106108d2cb48</t>
+          <t>https://www.indeed.com/viewjob?jk=60845048c5e70011</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895ccfdfabd80a00</t>
+          <t>https://www.indeed.com/viewjob?jk=36e72d3d377212ef</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60845048c5e70011</t>
+          <t>https://www.indeed.com/viewjob?jk=067a57b264a3d769</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e72d3d377212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=11c98ecd4628c5e9</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067a57b264a3d769</t>
+          <t>https://www.indeed.com/viewjob?jk=a65c027dc2ff5a07</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c98ecd4628c5e9</t>
+          <t>https://www.indeed.com/viewjob?jk=bf8e8d6efc4e8fd0</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65c027dc2ff5a07</t>
+          <t>https://www.indeed.com/viewjob?jk=1e49d76b2d69dfa2</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf8e8d6efc4e8fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=134d9282cf37a0ae</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e49d76b2d69dfa2</t>
+          <t>https://www.indeed.com/viewjob?jk=e72c66f56235b87a</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=134d9282cf37a0ae</t>
+          <t>https://www.indeed.com/viewjob?jk=331da26c68435ffe</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72c66f56235b87a</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85728be0a6515e</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=331da26c68435ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=dd873054d15e8766</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85728be0a6515e</t>
+          <t>https://www.indeed.com/viewjob?jk=6d86099ef8b381b8</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd873054d15e8766</t>
+          <t>https://www.indeed.com/viewjob?jk=f109e5071a47922c</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d86099ef8b381b8</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b6cd4f20194f69</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f109e5071a47922c</t>
+          <t>https://www.indeed.com/viewjob?jk=2649e457ca6d1f62</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b6cd4f20194f69</t>
+          <t>https://www.indeed.com/viewjob?jk=4c47e7783b37bb7f</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649e457ca6d1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea03bac31fda055</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c47e7783b37bb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=265ad9188f08d4fa</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea03bac31fda055</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc2bbb946ec5705</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265ad9188f08d4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9a888ebe473e5f</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc2bbb946ec5705</t>
+          <t>https://www.indeed.com/viewjob?jk=9872e02a1d0b5a55</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9a888ebe473e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a365d685f25643</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9872e02a1d0b5a55</t>
+          <t>https://www.indeed.com/viewjob?jk=7163db582e33e63f</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a365d685f25643</t>
+          <t>https://www.indeed.com/viewjob?jk=f4818ff983fe32be</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7163db582e33e63f</t>
+          <t>https://www.indeed.com/viewjob?jk=44025b0cc02106d4</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4818ff983fe32be</t>
+          <t>https://www.indeed.com/viewjob?jk=9b9169947786f5a4</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44025b0cc02106d4</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbbee3255a67262</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b9169947786f5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=a000d31ba2da0950</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbbee3255a67262</t>
+          <t>https://www.indeed.com/viewjob?jk=3eea0a491e9b49dd</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a000d31ba2da0950</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d0c7c3216eba93</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eea0a491e9b49dd</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5baa7bc18a6821</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d0c7c3216eba93</t>
+          <t>https://www.indeed.com/viewjob?jk=06b7ce759b03fc0a</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5baa7bc18a6821</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe68e26b4040f5d</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b7ce759b03fc0a</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf7a108004d0304</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe68e26b4040f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=48e2290ee4c4e6e9</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf7a108004d0304</t>
+          <t>https://www.indeed.com/viewjob?jk=b25498d222f29589</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e2290ee4c4e6e9</t>
+          <t>https://www.indeed.com/viewjob?jk=fe51a9b954fbdf0e</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b25498d222f29589</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1098dd2acf48ae</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe51a9b954fbdf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=d2934000541a09da</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1098dd2acf48ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9018daddfd9b2f20</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2934000541a09da</t>
+          <t>https://www.indeed.com/viewjob?jk=e290adebae65f2ae</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9018daddfd9b2f20</t>
+          <t>https://www.indeed.com/viewjob?jk=8556b0757d0f99dc</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Lynden</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>SeaTac, WA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e290adebae65f2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Senior Data Modeler - Mongo DB</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Kanan solutions</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556b0757d0f99dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
         </is>
       </c>
     </row>
@@ -3518,20 +3518,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lynden</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SeaTac, WA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
+          <t>https://www.indeed.com/viewjob?jk=7211706c4fa77eff</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Mongo DB</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kanan solutions</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, Databricks, Hadoop, HDFS, Hive, Spark, Scala, Kafka, ELT, MLOps</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer (Adobe Experience Platform)</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Merkle, Inc.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+          <t>AWS, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7211706c4fa77eff</t>
+          <t>https://www.indeed.com/viewjob?jk=f1893b5f6e215827</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Hive, Spark, Scala, Kafka, ELT, MLOps</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
+          <t>https://www.indeed.com/viewjob?jk=b76b7b194c7c6249</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CNH Industrial</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Sioux Falls, SD, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,34 +3671,34 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, Scala, ELT, CI/CD, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=46ac8fba1df212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=a6573882e75f2256</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Warehousing (Healthcare &amp; Life Sciences)</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,17 +3706,17 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, NoSQL</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=80268f7971251ec3</t>
+          <t>https://www.indeed.com/viewjob?jk=afbb42f1fb391e5b</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a21ae7255e004909</t>
+          <t>https://www.indeed.com/viewjob?jk=b4774424a7c977d0</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b76b7b194c7c6249</t>
+          <t>https://www.indeed.com/viewjob?jk=00673ec98ad396b2</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6573882e75f2256</t>
+          <t>https://www.indeed.com/viewjob?jk=0cca2406337e3f4b</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbb42f1fb391e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=9f87b401bf307b90</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4774424a7c977d0</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2545a3398f75f5</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00673ec98ad396b2</t>
+          <t>https://www.indeed.com/viewjob?jk=da5709f322b6de77</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cca2406337e3f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=33e7e2d41c6bbc1f</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f87b401bf307b90</t>
+          <t>https://www.indeed.com/viewjob?jk=2bbf8d425b26cb57</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2545a3398f75f5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8296a32cbcd5e8</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5709f322b6de77</t>
+          <t>https://www.indeed.com/viewjob?jk=bddcc0bf9a07cf52</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e7e2d41c6bbc1f</t>
+          <t>https://www.indeed.com/viewjob?jk=87c76b5382d91ff5</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bbf8d425b26cb57</t>
+          <t>https://www.indeed.com/viewjob?jk=e2a46dfdabaf144b</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8296a32cbcd5e8</t>
+          <t>https://www.indeed.com/viewjob?jk=148ea1e43d8803c0</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bddcc0bf9a07cf52</t>
+          <t>https://www.indeed.com/viewjob?jk=6d122abea15bffcd</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87c76b5382d91ff5</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb52081cc83a1d</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2a46dfdabaf144b</t>
+          <t>https://www.indeed.com/viewjob?jk=6585b0f7548a110e</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148ea1e43d8803c0</t>
+          <t>https://www.indeed.com/viewjob?jk=b6af657ad808aca0</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d122abea15bffcd</t>
+          <t>https://www.indeed.com/viewjob?jk=8c71c57379755325</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fb52081cc83a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4b1fb8cf73679e</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6585b0f7548a110e</t>
+          <t>https://www.indeed.com/viewjob?jk=eef37f19b519cfb3</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6af657ad808aca0</t>
+          <t>https://www.indeed.com/viewjob?jk=2acd943bf9f49043</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c71c57379755325</t>
+          <t>https://www.indeed.com/viewjob?jk=b5356ec2fad3097c</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4b1fb8cf73679e</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0b088c77b432bf</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef37f19b519cfb3</t>
+          <t>https://www.indeed.com/viewjob?jk=502c66caf2321daa</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2acd943bf9f49043</t>
+          <t>https://www.indeed.com/viewjob?jk=a8e35eb0472f1b04</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5356ec2fad3097c</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea808b55ddf87a1</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0b088c77b432bf</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d2fb8ee058fcb4</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=502c66caf2321daa</t>
+          <t>https://www.indeed.com/viewjob?jk=31e2d771ef37e989</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8e35eb0472f1b04</t>
+          <t>https://www.indeed.com/viewjob?jk=5701765b8810e954</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea808b55ddf87a1</t>
+          <t>https://www.indeed.com/viewjob?jk=a74fc9df8466ed80</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Upper Darby, PA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d2fb8ee058fcb4</t>
+          <t>https://www.indeed.com/viewjob?jk=e350cbedde8fb5c3</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e2d771ef37e989</t>
+          <t>https://www.indeed.com/viewjob?jk=37c3d1a6e3db03ea</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5701765b8810e954</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb7cf0d3892b335</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a74fc9df8466ed80</t>
+          <t>https://www.indeed.com/viewjob?jk=2515e91820622466</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e350cbedde8fb5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=9f92266e4f2da0ea</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37c3d1a6e3db03ea</t>
+          <t>https://www.indeed.com/viewjob?jk=5834a6a46819e223</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb7cf0d3892b335</t>
+          <t>https://www.indeed.com/viewjob?jk=a21ae7255e004909</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2515e91820622466</t>
+          <t>https://www.indeed.com/viewjob?jk=d766b034a172a2ae</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f92266e4f2da0ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab132d0ecb2e269</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5834a6a46819e223</t>
+          <t>https://www.indeed.com/viewjob?jk=163d580eae60a657</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d766b034a172a2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8d43b4208b386a</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab132d0ecb2e269</t>
+          <t>https://www.indeed.com/viewjob?jk=58a509ab2ac2911c</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163d580eae60a657</t>
+          <t>https://www.indeed.com/viewjob?jk=289f16a53bce28f8</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,139 +5246,139 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8d43b4208b386a</t>
+          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a509ab2ac2911c</t>
+          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289f16a53bce28f8</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>Arrive Logistics</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=4519eed0c0bcdda8</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=85cd0d74b3f6d1fd</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,34 +5421,34 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
+          <t>https://www.indeed.com/viewjob?jk=06a5cdb578318149</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Arrive Logistics</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, ETL, Python</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4519eed0c0bcdda8</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad4a5d391e5cb08</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>TrueScripts Management Services</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, IN, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85cd0d74b3f6d1fd</t>
+          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,17 +5526,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a5cdb578318149</t>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
         </is>
       </c>
     </row>
@@ -5548,12 +5548,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>La Jolla, CA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, ETL, Python</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad4a5d391e5cb08</t>
+          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TrueScripts Management Services</t>
+          <t>Palomar Holdings, Inc.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Washington, IN, US USA</t>
+          <t>Edina, MN, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Python/GenAI Solutions Architect</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=6ddb4f1cd1354de8</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Enterprise Architect</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Native American Industrial Solutions, LLC (NAIS)</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Wright-Patterson AFB, OH, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Analytics Engineer I</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Imperial PFS</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, Power BI, Tableau, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=70dd12166b6538af</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Python/GenAI Solutions Architect</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,244 +5771,244 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddb4f1cd1354de8</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Enterprise Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Native American Industrial Solutions, LLC (NAIS)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed0d719f5bbccf0</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Wright-Patterson AFB, OH, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
+          <t>https://www.indeed.com/viewjob?jk=69ed747f2eb90e25</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Analytics Data Engineer - Homes.com</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Power BI</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=b80d45c896bb26ef</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>Bed Bath &amp; Beyond</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>Google Cloud Platform, Hadoop, HBase, Spark, Scala, Kafka, Cassandra, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=4e18063e9579ba86</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Topeka, KS, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b18d9ee76a272912</t>
+          <t>https://www.indeed.com/viewjob?jk=dcea2f33a4118f28</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior Data Architect</t>
+          <t>Data Engineer- Greater Tampa</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Security Benefit</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, API Gateway, RDS, Snowflake, SQL Server, ELT</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec93e9305584f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed0d719f5bbccf0</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>NewYork-Presbyterian Hospital</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,34 +6051,34 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ed747f2eb90e25</t>
+          <t>https://www.indeed.com/viewjob?jk=cf557823600dd122</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Analytics Data Engineer - Homes.com</t>
+          <t>Software Engineer II (Backend, Platform)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Whoop</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,67 +6096,67 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80d45c896bb26ef</t>
+          <t>https://www.indeed.com/viewjob?jk=145abebc67be2858</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Senior Data Engineer - Data Quality and Governance</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Bed Bath &amp; Beyond</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Hadoop, HBase, Spark, Scala, Kafka, Cassandra, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e18063e9579ba86</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Data Engineer- Greater Tampa</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Estero, FL, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, Kinesis, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,94 +6166,94 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=c3cb1b92b52d7a99</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>CLAIR</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=62b06149f1d5d261</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend, Platform)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Whoop</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=145abebc67be2858</t>
+          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Quality and Governance</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Democratic National Committee</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Payments IT Business Analyst (AI &amp; Data Focus)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Estero, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cb1b92b52d7a99</t>
+          <t>https://www.indeed.com/viewjob?jk=6e859637db4511ad</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>CLAIR</t>
+          <t>Pacific Consulting</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Salem, VA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62b06149f1d5d261</t>
+          <t>https://www.indeed.com/viewjob?jk=0e8bd5938a7b9489</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
+          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Democratic National Committee</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,34 +6401,34 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=d45183e5b3bce9f1</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Data Engineer - North America Fabric Care</t>
+          <t>VIE - Software Engineer (based in Miami)</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Procter &amp; Gamble</t>
+          <t>Pelico</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, GCP, Spark, PySpark, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bda137520545caf7</t>
+          <t>https://www.indeed.com/viewjob?jk=072180860b5c5965</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior Payments IT Business Analyst (AI &amp; Data Focus)</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,155 +6471,15 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6e859637db4511ad</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Systems Administrator</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>Pacific Consulting</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Salem, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, SQL</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e8bd5938a7b9489</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Alliance Health Plan</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Morrisville, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>VIE - Software Engineer (based in Miami)</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Pelico</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2025-10-07</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=072180860b5c5965</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>American Airlines</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
         </is>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G173"/>
+  <dimension ref="A1:G175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -748,35 +748,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer – Streaming, Analytics &amp; Visualization</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Seamless</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, RDS, Azure, Data Factory, Medallion Architecture, GCP, BigQuery, Scala</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=40021f9da2941e8e</t>
+          <t>https://www.indeed.com/viewjob?jk=478c9b428f7558f4</t>
         </is>
       </c>
     </row>
@@ -1483,7 +1483,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior RAPA Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,34 +1501,34 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=e20027a6a5bcf1cf</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,17 +1536,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1f698284725984</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb838c30917dc45</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1f698284725984</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e506811c0b2cc445</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb838c30917dc45</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18381d7ceeaba33a</t>
+          <t>https://www.indeed.com/viewjob?jk=e506811c0b2cc445</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcc2deee2a3e4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=18381d7ceeaba33a</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Technology Specialist II - Data Architect - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ca165a02301fbf</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc2deee2a3e4d7</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Technology Specialist II - Data Architect - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403061dcf440ec37</t>
+          <t>https://www.indeed.com/viewjob?jk=31ca165a02301fbf</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f4a1c92a28581b</t>
+          <t>https://www.indeed.com/viewjob?jk=403061dcf440ec37</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=534a121db23077a6</t>
+          <t>https://www.indeed.com/viewjob?jk=99f4a1c92a28581b</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845609474cda1ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=534a121db23077a6</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bac106108d2cb48</t>
+          <t>https://www.indeed.com/viewjob?jk=845609474cda1ceb</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895ccfdfabd80a00</t>
+          <t>https://www.indeed.com/viewjob?jk=7bac106108d2cb48</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60845048c5e70011</t>
+          <t>https://www.indeed.com/viewjob?jk=895ccfdfabd80a00</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e72d3d377212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=60845048c5e70011</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067a57b264a3d769</t>
+          <t>https://www.indeed.com/viewjob?jk=36e72d3d377212ef</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c98ecd4628c5e9</t>
+          <t>https://www.indeed.com/viewjob?jk=067a57b264a3d769</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65c027dc2ff5a07</t>
+          <t>https://www.indeed.com/viewjob?jk=11c98ecd4628c5e9</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf8e8d6efc4e8fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=a65c027dc2ff5a07</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e49d76b2d69dfa2</t>
+          <t>https://www.indeed.com/viewjob?jk=bf8e8d6efc4e8fd0</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=134d9282cf37a0ae</t>
+          <t>https://www.indeed.com/viewjob?jk=1e49d76b2d69dfa2</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72c66f56235b87a</t>
+          <t>https://www.indeed.com/viewjob?jk=134d9282cf37a0ae</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=331da26c68435ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=e72c66f56235b87a</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85728be0a6515e</t>
+          <t>https://www.indeed.com/viewjob?jk=331da26c68435ffe</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd873054d15e8766</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85728be0a6515e</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d86099ef8b381b8</t>
+          <t>https://www.indeed.com/viewjob?jk=dd873054d15e8766</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f109e5071a47922c</t>
+          <t>https://www.indeed.com/viewjob?jk=6d86099ef8b381b8</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b6cd4f20194f69</t>
+          <t>https://www.indeed.com/viewjob?jk=f109e5071a47922c</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649e457ca6d1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b6cd4f20194f69</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c47e7783b37bb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=2649e457ca6d1f62</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea03bac31fda055</t>
+          <t>https://www.indeed.com/viewjob?jk=4c47e7783b37bb7f</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265ad9188f08d4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea03bac31fda055</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc2bbb946ec5705</t>
+          <t>https://www.indeed.com/viewjob?jk=265ad9188f08d4fa</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9a888ebe473e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc2bbb946ec5705</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9872e02a1d0b5a55</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9a888ebe473e5f</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a365d685f25643</t>
+          <t>https://www.indeed.com/viewjob?jk=9872e02a1d0b5a55</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7163db582e33e63f</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a365d685f25643</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4818ff983fe32be</t>
+          <t>https://www.indeed.com/viewjob?jk=7163db582e33e63f</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44025b0cc02106d4</t>
+          <t>https://www.indeed.com/viewjob?jk=f4818ff983fe32be</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b9169947786f5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=44025b0cc02106d4</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbbee3255a67262</t>
+          <t>https://www.indeed.com/viewjob?jk=9b9169947786f5a4</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a000d31ba2da0950</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbbee3255a67262</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eea0a491e9b49dd</t>
+          <t>https://www.indeed.com/viewjob?jk=a000d31ba2da0950</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d0c7c3216eba93</t>
+          <t>https://www.indeed.com/viewjob?jk=3eea0a491e9b49dd</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5baa7bc18a6821</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d0c7c3216eba93</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b7ce759b03fc0a</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5baa7bc18a6821</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe68e26b4040f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=06b7ce759b03fc0a</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf7a108004d0304</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe68e26b4040f5d</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e2290ee4c4e6e9</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf7a108004d0304</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b25498d222f29589</t>
+          <t>https://www.indeed.com/viewjob?jk=48e2290ee4c4e6e9</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe51a9b954fbdf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=b25498d222f29589</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1098dd2acf48ae</t>
+          <t>https://www.indeed.com/viewjob?jk=fe51a9b954fbdf0e</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2934000541a09da</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1098dd2acf48ae</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9018daddfd9b2f20</t>
+          <t>https://www.indeed.com/viewjob?jk=d2934000541a09da</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e290adebae65f2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9018daddfd9b2f20</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556b0757d0f99dc</t>
+          <t>https://www.indeed.com/viewjob?jk=e290adebae65f2ae</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Lynden</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>SeaTac, WA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
+          <t>https://www.indeed.com/viewjob?jk=8556b0757d0f99dc</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Mongo DB</t>
+          <t>GIS Software Engineer - Esri</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Kanan solutions</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,17 +3496,17 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
+          <t>https://www.indeed.com/viewjob?jk=21ac825d5b64f66f</t>
         </is>
       </c>
     </row>
@@ -3518,20 +3518,20 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Lynden</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>SeaTac, WA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7211706c4fa77eff</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Data Modeler - Mongo DB</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Kanan solutions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Hive, Spark, Scala, Kafka, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
+          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer (Adobe Experience Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Merkle, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1893b5f6e215827</t>
+          <t>https://www.indeed.com/viewjob?jk=7211706c4fa77eff</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,34 +3636,34 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Databricks, Hadoop, HDFS, Hive, Spark, Scala, Kafka, ELT, MLOps</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b76b7b194c7c6249</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data Engineer (Adobe Experience Platform)</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Merkle, Inc.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6573882e75f2256</t>
+          <t>https://www.indeed.com/viewjob?jk=f1893b5f6e215827</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbb42f1fb391e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=b76b7b194c7c6249</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4774424a7c977d0</t>
+          <t>https://www.indeed.com/viewjob?jk=a6573882e75f2256</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00673ec98ad396b2</t>
+          <t>https://www.indeed.com/viewjob?jk=afbb42f1fb391e5b</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cca2406337e3f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=b4774424a7c977d0</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f87b401bf307b90</t>
+          <t>https://www.indeed.com/viewjob?jk=00673ec98ad396b2</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2545a3398f75f5</t>
+          <t>https://www.indeed.com/viewjob?jk=0cca2406337e3f4b</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5709f322b6de77</t>
+          <t>https://www.indeed.com/viewjob?jk=9f87b401bf307b90</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e7e2d41c6bbc1f</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2545a3398f75f5</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bbf8d425b26cb57</t>
+          <t>https://www.indeed.com/viewjob?jk=da5709f322b6de77</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8296a32cbcd5e8</t>
+          <t>https://www.indeed.com/viewjob?jk=33e7e2d41c6bbc1f</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bddcc0bf9a07cf52</t>
+          <t>https://www.indeed.com/viewjob?jk=2bbf8d425b26cb57</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87c76b5382d91ff5</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8296a32cbcd5e8</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2a46dfdabaf144b</t>
+          <t>https://www.indeed.com/viewjob?jk=bddcc0bf9a07cf52</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148ea1e43d8803c0</t>
+          <t>https://www.indeed.com/viewjob?jk=87c76b5382d91ff5</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d122abea15bffcd</t>
+          <t>https://www.indeed.com/viewjob?jk=e2a46dfdabaf144b</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fb52081cc83a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=148ea1e43d8803c0</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6585b0f7548a110e</t>
+          <t>https://www.indeed.com/viewjob?jk=6d122abea15bffcd</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6af657ad808aca0</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb52081cc83a1d</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c71c57379755325</t>
+          <t>https://www.indeed.com/viewjob?jk=6585b0f7548a110e</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4b1fb8cf73679e</t>
+          <t>https://www.indeed.com/viewjob?jk=b6af657ad808aca0</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef37f19b519cfb3</t>
+          <t>https://www.indeed.com/viewjob?jk=8c71c57379755325</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2acd943bf9f49043</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4b1fb8cf73679e</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5356ec2fad3097c</t>
+          <t>https://www.indeed.com/viewjob?jk=eef37f19b519cfb3</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0b088c77b432bf</t>
+          <t>https://www.indeed.com/viewjob?jk=2acd943bf9f49043</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=502c66caf2321daa</t>
+          <t>https://www.indeed.com/viewjob?jk=b5356ec2fad3097c</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8e35eb0472f1b04</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0b088c77b432bf</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea808b55ddf87a1</t>
+          <t>https://www.indeed.com/viewjob?jk=502c66caf2321daa</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d2fb8ee058fcb4</t>
+          <t>https://www.indeed.com/viewjob?jk=a8e35eb0472f1b04</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e2d771ef37e989</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea808b55ddf87a1</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5701765b8810e954</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d2fb8ee058fcb4</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a74fc9df8466ed80</t>
+          <t>https://www.indeed.com/viewjob?jk=31e2d771ef37e989</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e350cbedde8fb5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=5701765b8810e954</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37c3d1a6e3db03ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a74fc9df8466ed80</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Upper Darby, PA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb7cf0d3892b335</t>
+          <t>https://www.indeed.com/viewjob?jk=e350cbedde8fb5c3</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2515e91820622466</t>
+          <t>https://www.indeed.com/viewjob?jk=37c3d1a6e3db03ea</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f92266e4f2da0ea</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb7cf0d3892b335</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5834a6a46819e223</t>
+          <t>https://www.indeed.com/viewjob?jk=2515e91820622466</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a21ae7255e004909</t>
+          <t>https://www.indeed.com/viewjob?jk=9f92266e4f2da0ea</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d766b034a172a2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=5834a6a46819e223</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab132d0ecb2e269</t>
+          <t>https://www.indeed.com/viewjob?jk=a21ae7255e004909</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163d580eae60a657</t>
+          <t>https://www.indeed.com/viewjob?jk=d766b034a172a2ae</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8d43b4208b386a</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab132d0ecb2e269</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a509ab2ac2911c</t>
+          <t>https://www.indeed.com/viewjob?jk=163d580eae60a657</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289f16a53bce28f8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8d43b4208b386a</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,77 +5246,77 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=58a509ab2ac2911c</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=289f16a53bce28f8</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
+          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Arrive Logistics</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,34 +5351,34 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4519eed0c0bcdda8</t>
+          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,34 +5386,34 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85cd0d74b3f6d1fd</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a5cdb578318149</t>
+          <t>https://www.indeed.com/viewjob?jk=fb076bf063bb2a72</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Arrive Logistics</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, ETL, Python</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad4a5d391e5cb08</t>
+          <t>https://www.indeed.com/viewjob?jk=4519eed0c0bcdda8</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>TrueScripts Management Services</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Washington, IN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,34 +5491,34 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+          <t>https://www.indeed.com/viewjob?jk=85cd0d74b3f6d1fd</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,17 +5526,17 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=06a5cdb578318149</t>
         </is>
       </c>
     </row>
@@ -5548,12 +5548,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>La Jolla, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,34 +5561,34 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, ETL, Python</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3ba8acc35014037</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad4a5d391e5cb08</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Palomar Holdings, Inc.</t>
+          <t>TrueScripts Management Services</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Edina, MN, US USA</t>
+          <t>Washington, IN, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cb74b7d64f89d93</t>
+          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Python/GenAI Solutions Architect</t>
+          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Lockheed Martin</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>King of Prussia, PA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,34 +5631,34 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddb4f1cd1354de8</t>
+          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Senior Enterprise Architect</t>
+          <t>Python/GenAI Solutions Architect</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Native American Industrial Solutions, LLC (NAIS)</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,34 +5666,34 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
+          <t>https://www.indeed.com/viewjob?jk=6ddb4f1cd1354de8</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Enterprise Architect</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>Native American Industrial Solutions, LLC (NAIS)</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Wright-Patterson AFB, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
+          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Wright-Patterson AFB, OH, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,42 +5781,42 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Data Modeling, ETL</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed0d719f5bbccf0</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ed747f2eb90e25</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed0d719f5bbccf0</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Senior Analytics Data Engineer - Homes.com</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Power BI</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80d45c896bb26ef</t>
+          <t>https://www.indeed.com/viewjob?jk=69ed747f2eb90e25</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Senior Analytics Data Engineer - Homes.com</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Bed Bath &amp; Beyond</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Hadoop, HBase, Spark, Scala, Kafka, Cassandra, Docker, Kubernetes, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Power BI</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e18063e9579ba86</t>
+          <t>https://www.indeed.com/viewjob?jk=b80d45c896bb26ef</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer II</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Bed Bath &amp; Beyond</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>Google Cloud Platform, Hadoop, HBase, Spark, Scala, Kafka, Cassandra, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcea2f33a4118f28</t>
+          <t>https://www.indeed.com/viewjob?jk=4e18063e9579ba86</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Data Engineer- Greater Tampa</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=dcea2f33a4118f28</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Data Engineer- Greater Tampa</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,34 +6016,34 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>NewYork-Presbyterian Hospital</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,34 +6051,34 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf557823600dd122</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend, Platform)</t>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Whoop</t>
+          <t>NewYork-Presbyterian Hospital</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,69 +6086,69 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=145abebc67be2858</t>
+          <t>https://www.indeed.com/viewjob?jk=cf557823600dd122</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Quality and Governance</t>
+          <t>Software Engineer II (Backend, Platform)</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Whoop</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
+          <t>https://www.indeed.com/viewjob?jk=145abebc67be2858</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer - Data Quality and Governance</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Estero, FL, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,34 +6156,34 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cb1b92b52d7a99</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>CLAIR</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Estero, FL, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt, Airflow</t>
+          <t>AWS, Kinesis, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62b06149f1d5d261</t>
+          <t>https://www.indeed.com/viewjob?jk=c3cb1b92b52d7a99</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>CLAIR</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,34 +6226,34 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
+          <t>https://www.indeed.com/viewjob?jk=62b06149f1d5d261</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Democratic National Committee</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior Payments IT Business Analyst (AI &amp; Data Focus)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>Democratic National Committee</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,17 +6296,17 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Power BI, Tableau</t>
+          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e859637db4511ad</t>
+          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
         </is>
       </c>
     </row>
@@ -6318,12 +6318,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Pacific Consulting</t>
+          <t>EPODIUM</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Salem, VA, US USA</t>
+          <t>Tacoma, WA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, SQL</t>
+          <t>AWS, RDS, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e8bd5938a7b9489</t>
+          <t>https://www.indeed.com/viewjob?jk=7bacca274417a8a0</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
+          <t>Senior Payments IT Business Analyst (AI &amp; Data Focus)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=6e859637db4511ad</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Pacific Consulting</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Salem, VA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, SQL</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45183e5b3bce9f1</t>
+          <t>https://www.indeed.com/viewjob?jk=0e8bd5938a7b9489</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>VIE - Software Engineer (based in Miami)</t>
+          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Pelico</t>
+          <t>Alliance Health Plan</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Morrisville, NC, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,34 +6436,34 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072180860b5c5965</t>
+          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Goldman Sachs</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,15 +6471,85 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d45183e5b3bce9f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>VIE - Software Engineer (based in Miami)</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Pelico</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=072180860b5c5965</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
           <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F173" t="inlineStr">
+      <c r="F175" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
+      <c r="G175" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
         </is>

--- a/results/job_matches_2026-08-18.xlsx
+++ b/results/job_matches_2026-08-18.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G175"/>
+  <dimension ref="A1:G182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Software Developer - Meter Data Management Software (Full Stack, Back End)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>National Information Solutions Cooperative (NISC)</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,34 +591,34 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, S3, SQS, SNS, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, Snowflake, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1fae15aac6f86c7</t>
+          <t>https://www.indeed.com/viewjob?jk=93c578df954821f2</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI Cloud Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -626,7 +626,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, ECS, IAM, Snowflake, SQL Server, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93c578df954821f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5c52720211e7a971</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior AI Cloud Solutions Architect</t>
+          <t>Software Engineer III, AI Digital &amp; Engineering Software</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>X-Energy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, ECS, IAM, RDS, Azure, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c52720211e7a971</t>
+          <t>https://www.indeed.com/viewjob?jk=724dd35cc9ba9c68</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer III, AI Digital &amp; Engineering Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>X-Energy</t>
+          <t>Veridic Solutions</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, S3, API Gateway, ECS, IAM, RDS</t>
+          <t>AWS, Redshift, Azure, Synapse Analytics, BigQuery, Scala, Snowflake, SQL Server, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=724dd35cc9ba9c68</t>
+          <t>https://www.indeed.com/viewjob?jk=5dc73ec2502e27a3</t>
         </is>
       </c>
     </row>
@@ -718,20 +718,20 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Veridic Solutions</t>
+          <t>Seamless</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Synapse Analytics, BigQuery, Scala, Snowflake, SQL Server, MySQL, MongoDB</t>
+          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dc73ec2502e27a3</t>
+          <t>https://www.indeed.com/viewjob?jk=478c9b428f7558f4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Seamless</t>
+          <t>Textron</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Step Functions, S3, RDS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Scala, Snowflake, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=478c9b428f7558f4</t>
+          <t>https://www.indeed.com/viewjob?jk=89e3a0d656748e7c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>DATA MANAGEMENT ENGINEER – Full Stack</t>
+          <t>Product Owner - Cloud Contact Center (CCaaS) &amp; Data Platform</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BNY</t>
+          <t>Betsol</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Broomfield, CO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RDS, Azure, Hadoop, Hive, Spark, Scala, Snowflake, Oracle, SQL Server, ETL</t>
+          <t>AWS, Glue, Lambda, Redshift, SQS, SNS, IAM, RDS, Azure, Data Factory</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7fb8f75345ac6681</t>
+          <t>https://www.indeed.com/viewjob?jk=8bd7071de6b014d4</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - AI</t>
+          <t>Intern 2027 - Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Dairy Farmers of America, Inc.</t>
+          <t>LPL Financial</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Google Cloud Platform, GCP, BigQuery, Spark, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
+          <t>https://www.indeed.com/viewjob?jk=22be3c305311c8c5</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Sr. Software Development Engineer</t>
+          <t>Sr. Data Engineer - AI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Dairy Farmers of America, Inc.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Scala, Oracle, MySQL, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5d92ba9e6d3e13</t>
+          <t>https://www.indeed.com/viewjob?jk=564a930b352284d3</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
+          <t>Data Modeler</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TDIndustries</t>
+          <t>CSpring</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Springfield, IL, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,42 +906,42 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Snowflake, Databricks Lakehouse, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
+          <t>https://www.indeed.com/viewjob?jk=61541eff4b55a7f4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Sr. Software Development Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JACK Entertainment</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hive, Scala, Oracle, MySQL, Cassandra</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,59 +951,59 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ddeffbcda3a30081</t>
+          <t>https://www.indeed.com/viewjob?jk=da5d92ba9e6d3e13</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Solution Architect - Data, Analytics &amp; AI</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Plymouth Rock Assurance</t>
+          <t>TDIndustries</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Medallion Architecture, Dataflow, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=abd794d42375295b</t>
+          <t>https://www.indeed.com/viewjob?jk=8ac8a616958996b3</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>JACK Entertainment</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, BigQuery, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e97bf8ea06c2dcbb</t>
+          <t>https://www.indeed.com/viewjob?jk=ddeffbcda3a30081</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ISOD Limited</t>
+          <t>Plymouth Rock Assurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, Snowflake, Data Modeling, ETL, ELT, Tableau</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=91f52b29094f2ea2</t>
+          <t>https://www.indeed.com/viewjob?jk=abd794d42375295b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior SAP Sales and Service Cloud Consultant</t>
+          <t>US- Java Engineer - Pricing</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Data Solutions LLC</t>
+          <t>MoneyGram</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, HBase, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
+          <t>https://www.indeed.com/viewjob?jk=5191a2ca13d017d5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>US- Java Engineer - Pricing</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>MoneyGram</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, HBase, Kafka, Oracle</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd78528f3cfeae1</t>
+          <t>https://www.indeed.com/viewjob?jk=6cc05afa82c7727d</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
+          <t>AWS, S3, RDS, Databricks, Hadoop, HDFS, Hive, Impala, Spark, PySpark</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a03747dc8123c18e</t>
+          <t>https://www.indeed.com/viewjob?jk=e97bf8ea06c2dcbb</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer (Microsoft Azure)</t>
+          <t>Senior Data Scientist – Machine Learning &amp; AI</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Team Velocity Marketing</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Herndon, VA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Azure, GCP, Vertex AI, Spark, Scala, Snowflake, dbt, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,32 +1196,32 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a0b93ee4cad8277</t>
+          <t>https://www.indeed.com/viewjob?jk=4835e886da15e697</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Palantir Data engineer - Forward Deployment Engineers</t>
+          <t>Senior Full Stack Developer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>AI SPINS INC</t>
+          <t>ISOD Limited</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Azure, Databricks, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a35bc9c9058b4a38</t>
+          <t>https://www.indeed.com/viewjob?jk=91f52b29094f2ea2</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior SAP Sales and Service Cloud Consultant</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Tripoint Solutions</t>
+          <t>Data Solutions LLC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
+          <t>https://www.indeed.com/viewjob?jk=7e9a9f7e834d9af9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=695b8a15f31b95e9</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd78528f3cfeae1</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Spark, Scala</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0d45121b0e1810c1</t>
+          <t>https://www.indeed.com/viewjob?jk=a03747dc8123c18e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Data Engineer (Microsoft Azure)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Cloud Storage, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f609822c97459ef7</t>
+          <t>https://www.indeed.com/viewjob?jk=7a0b93ee4cad8277</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Palantir Data engineer - Forward Deployment Engineers</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>AI SPINS INC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Redshift, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, BigQuery</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3500a77261ebbb93</t>
+          <t>https://www.indeed.com/viewjob?jk=a35bc9c9058b4a38</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Python Developer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Tripoint Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Redshift, S3, SNS, ECS, IAM, RDS, Scala, ELT, Splunk</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a07575a9e0364be</t>
+          <t>https://www.indeed.com/viewjob?jk=7efa743be477c307</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr Machine Learning Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e622b2e76eb112c1</t>
+          <t>https://www.indeed.com/viewjob?jk=695b8a15f31b95e9</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior RAPA Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,49 +1511,49 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e20027a6a5bcf1cf</t>
+          <t>https://www.indeed.com/viewjob?jk=0d45121b0e1810c1</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Elmhurst, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
+          <t>https://www.indeed.com/viewjob?jk=f609822c97459ef7</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1563,15 +1563,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f1f698284725984</t>
+          <t>https://www.indeed.com/viewjob?jk=3500a77261ebbb93</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Python Developer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,15 +1598,15 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5bb838c30917dc45</t>
+          <t>https://www.indeed.com/viewjob?jk=5a07575a9e0364be</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, CI/CD, Jenkins, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e506811c0b2cc445</t>
+          <t>https://www.indeed.com/viewjob?jk=e622b2e76eb112c1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Senior RAPA Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>RDS, Azure, Data Factory, Scala, Snowflake, ETL, ELT, dbt, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18381d7ceeaba33a</t>
+          <t>https://www.indeed.com/viewjob?jk=e20027a6a5bcf1cf</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Elmhurst, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, API Gateway, IAM, RDS, DynamoDB, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcc2deee2a3e4d7</t>
+          <t>https://www.indeed.com/viewjob?jk=84c7ccd0aea4cc19</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Technology Specialist II - Data Architect - Digital and Technology Partners - Hybrid/Remote</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mount Sinai Health System</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Scala, Oracle, SQL Server, MySQL, MongoDB, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31ca165a02301fbf</t>
+          <t>https://www.indeed.com/viewjob?jk=2227dc402960acc4</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=403061dcf440ec37</t>
+          <t>https://www.indeed.com/viewjob?jk=7f1f698284725984</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=99f4a1c92a28581b</t>
+          <t>https://www.indeed.com/viewjob?jk=5bb838c30917dc45</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=534a121db23077a6</t>
+          <t>https://www.indeed.com/viewjob?jk=e506811c0b2cc445</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845609474cda1ceb</t>
+          <t>https://www.indeed.com/viewjob?jk=18381d7ceeaba33a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Hive, Spark, Snowflake, Oracle, SQL Server, MongoDB, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bac106108d2cb48</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcc2deee2a3e4d7</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Engineer - Observability Platform</t>
+          <t>Technology Specialist II - Data Architect - Digital and Technology Partners - Hybrid/Remote</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Mount Sinai Health System</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Data Factory, Databricks, Hadoop, Spark, Scala, Kafka, Oracle, PostgreSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=895ccfdfabd80a00</t>
+          <t>https://www.indeed.com/viewjob?jk=31ca165a02301fbf</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60845048c5e70011</t>
+          <t>https://www.indeed.com/viewjob?jk=403061dcf440ec37</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36e72d3d377212ef</t>
+          <t>https://www.indeed.com/viewjob?jk=99f4a1c92a28581b</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=067a57b264a3d769</t>
+          <t>https://www.indeed.com/viewjob?jk=534a121db23077a6</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11c98ecd4628c5e9</t>
+          <t>https://www.indeed.com/viewjob?jk=845609474cda1ceb</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a65c027dc2ff5a07</t>
+          <t>https://www.indeed.com/viewjob?jk=7bac106108d2cb48</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf8e8d6efc4e8fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=895ccfdfabd80a00</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e49d76b2d69dfa2</t>
+          <t>https://www.indeed.com/viewjob?jk=60845048c5e70011</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=134d9282cf37a0ae</t>
+          <t>https://www.indeed.com/viewjob?jk=36e72d3d377212ef</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e72c66f56235b87a</t>
+          <t>https://www.indeed.com/viewjob?jk=067a57b264a3d769</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=331da26c68435ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=11c98ecd4628c5e9</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea85728be0a6515e</t>
+          <t>https://www.indeed.com/viewjob?jk=a65c027dc2ff5a07</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd873054d15e8766</t>
+          <t>https://www.indeed.com/viewjob?jk=bf8e8d6efc4e8fd0</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d86099ef8b381b8</t>
+          <t>https://www.indeed.com/viewjob?jk=1e49d76b2d69dfa2</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f109e5071a47922c</t>
+          <t>https://www.indeed.com/viewjob?jk=134d9282cf37a0ae</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d7b6cd4f20194f69</t>
+          <t>https://www.indeed.com/viewjob?jk=e72c66f56235b87a</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2649e457ca6d1f62</t>
+          <t>https://www.indeed.com/viewjob?jk=331da26c68435ffe</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c47e7783b37bb7f</t>
+          <t>https://www.indeed.com/viewjob?jk=ea85728be0a6515e</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ea03bac31fda055</t>
+          <t>https://www.indeed.com/viewjob?jk=dd873054d15e8766</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=265ad9188f08d4fa</t>
+          <t>https://www.indeed.com/viewjob?jk=6d86099ef8b381b8</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9dc2bbb946ec5705</t>
+          <t>https://www.indeed.com/viewjob?jk=f109e5071a47922c</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd9a888ebe473e5f</t>
+          <t>https://www.indeed.com/viewjob?jk=d7b6cd4f20194f69</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9872e02a1d0b5a55</t>
+          <t>https://www.indeed.com/viewjob?jk=2649e457ca6d1f62</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4a365d685f25643</t>
+          <t>https://www.indeed.com/viewjob?jk=4c47e7783b37bb7f</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7163db582e33e63f</t>
+          <t>https://www.indeed.com/viewjob?jk=0ea03bac31fda055</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4818ff983fe32be</t>
+          <t>https://www.indeed.com/viewjob?jk=265ad9188f08d4fa</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44025b0cc02106d4</t>
+          <t>https://www.indeed.com/viewjob?jk=9dc2bbb946ec5705</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b9169947786f5a4</t>
+          <t>https://www.indeed.com/viewjob?jk=dd9a888ebe473e5f</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dbbee3255a67262</t>
+          <t>https://www.indeed.com/viewjob?jk=9872e02a1d0b5a55</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a000d31ba2da0950</t>
+          <t>https://www.indeed.com/viewjob?jk=b4a365d685f25643</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3eea0a491e9b49dd</t>
+          <t>https://www.indeed.com/viewjob?jk=7163db582e33e63f</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d0c7c3216eba93</t>
+          <t>https://www.indeed.com/viewjob?jk=f4818ff983fe32be</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e5baa7bc18a6821</t>
+          <t>https://www.indeed.com/viewjob?jk=44025b0cc02106d4</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06b7ce759b03fc0a</t>
+          <t>https://www.indeed.com/viewjob?jk=9b9169947786f5a4</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbe68e26b4040f5d</t>
+          <t>https://www.indeed.com/viewjob?jk=1dbbee3255a67262</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1cf7a108004d0304</t>
+          <t>https://www.indeed.com/viewjob?jk=a000d31ba2da0950</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48e2290ee4c4e6e9</t>
+          <t>https://www.indeed.com/viewjob?jk=3eea0a491e9b49dd</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b25498d222f29589</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d0c7c3216eba93</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe51a9b954fbdf0e</t>
+          <t>https://www.indeed.com/viewjob?jk=4e5baa7bc18a6821</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1098dd2acf48ae</t>
+          <t>https://www.indeed.com/viewjob?jk=06b7ce759b03fc0a</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d2934000541a09da</t>
+          <t>https://www.indeed.com/viewjob?jk=dbe68e26b4040f5d</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9018daddfd9b2f20</t>
+          <t>https://www.indeed.com/viewjob?jk=1cf7a108004d0304</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e290adebae65f2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=48e2290ee4c4e6e9</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8556b0757d0f99dc</t>
+          <t>https://www.indeed.com/viewjob?jk=b25498d222f29589</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>GIS Software Engineer - Esri</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>The Hartford</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21ac825d5b64f66f</t>
+          <t>https://www.indeed.com/viewjob?jk=fe51a9b954fbdf0e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lynden</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>SeaTac, WA, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
+          <t>https://www.indeed.com/viewjob?jk=bc1098dd2acf48ae</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Modeler - Mongo DB</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Kanan solutions</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,24 +3566,24 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
+          <t>https://www.indeed.com/viewjob?jk=d2934000541a09da</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3593,15 +3593,15 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,67 +3611,67 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7211706c4fa77eff</t>
+          <t>https://www.indeed.com/viewjob?jk=9018daddfd9b2f20</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Hadoop, HDFS, Hive, Spark, Scala, Kafka, ELT, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
+          <t>https://www.indeed.com/viewjob?jk=e290adebae65f2ae</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer (Adobe Experience Platform)</t>
+          <t>Senior Engineer - Observability Platform</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Merkle, Inc.</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, dbt, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Kafka, PostgreSQL, MySQL, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1893b5f6e215827</t>
+          <t>https://www.indeed.com/viewjob?jk=8556b0757d0f99dc</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Database Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Scala, PostgreSQL, Cassandra, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b76b7b194c7c6249</t>
+          <t>https://www.indeed.com/viewjob?jk=603d527a2d1773a6</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>GIS Software Engineer - Esri</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>The Hartford</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Long Key, FL, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, API Gateway, RDS, Scala, Snowflake, Oracle, SQL Server, PostgreSQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6573882e75f2256</t>
+          <t>https://www.indeed.com/viewjob?jk=21ac825d5b64f66f</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Lynden</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>SeaTac, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>RDS, Azure, Data Factory, Data Lake Storage, Event Hubs, Medallion Architecture, Spark, PySpark, Scala, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,59 +3786,59 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afbb42f1fb391e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=8cf81bd1ef4f9ea4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Data Modeler - Mongo DB</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Kanan solutions</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Montpelier, VT, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MongoDB, NoSQL, Data Modeling, Snowflake Schema</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4774424a7c977d0</t>
+          <t>https://www.indeed.com/viewjob?jk=b821d85e7c3f3fda</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Des Moines, IA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, HDFS, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00673ec98ad396b2</t>
+          <t>https://www.indeed.com/viewjob?jk=7211706c4fa77eff</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,34 +3881,34 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Databricks, Hadoop, HDFS, Hive, Spark, Scala, Kafka, ELT, MLOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0cca2406337e3f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=6bfbd27edc96381f</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
+          <t>Data Engineer (Adobe Experience Platform)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CSAA Insurance Group, a AAA Insurer</t>
+          <t>Merkle, Inc.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Lincoln, NE, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
+          <t>AWS, Databricks, BigQuery, Spark, PySpark, Scala, Snowflake, dbt, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f87b401bf307b90</t>
+          <t>https://www.indeed.com/viewjob?jk=f1893b5f6e215827</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e2545a3398f75f5</t>
+          <t>https://www.indeed.com/viewjob?jk=b76b7b194c7c6249</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Long Key, FL, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=da5709f322b6de77</t>
+          <t>https://www.indeed.com/viewjob?jk=a6573882e75f2256</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Pierre, SD, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e7e2d41c6bbc1f</t>
+          <t>https://www.indeed.com/viewjob?jk=afbb42f1fb391e5b</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Montpelier, VT, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2bbf8d425b26cb57</t>
+          <t>https://www.indeed.com/viewjob?jk=b4774424a7c977d0</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5d8296a32cbcd5e8</t>
+          <t>https://www.indeed.com/viewjob?jk=00673ec98ad396b2</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Hope Hull, AL, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bddcc0bf9a07cf52</t>
+          <t>https://www.indeed.com/viewjob?jk=0cca2406337e3f4b</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Lincoln, NE, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=87c76b5382d91ff5</t>
+          <t>https://www.indeed.com/viewjob?jk=9f87b401bf307b90</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Pawtucket, RI, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2a46dfdabaf144b</t>
+          <t>https://www.indeed.com/viewjob?jk=1e2545a3398f75f5</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Hot Springs Village, AR, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148ea1e43d8803c0</t>
+          <t>https://www.indeed.com/viewjob?jk=da5709f322b6de77</t>
         </is>
       </c>
     </row>
@@ -4258,7 +4258,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Jackson, MS, US USA</t>
+          <t>Pierre, SD, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4276,7 +4276,7 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d122abea15bffcd</t>
+          <t>https://www.indeed.com/viewjob?jk=33e7e2d41c6bbc1f</t>
         </is>
       </c>
     </row>
@@ -4293,7 +4293,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Middletown, DE, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4311,7 +4311,7 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b9fb52081cc83a1d</t>
+          <t>https://www.indeed.com/viewjob?jk=2bbf8d425b26cb57</t>
         </is>
       </c>
     </row>
@@ -4328,7 +4328,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6585b0f7548a110e</t>
+          <t>https://www.indeed.com/viewjob?jk=5d8296a32cbcd5e8</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4363,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Hope Hull, AL, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6af657ad808aca0</t>
+          <t>https://www.indeed.com/viewjob?jk=bddcc0bf9a07cf52</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Charleston, WV, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c71c57379755325</t>
+          <t>https://www.indeed.com/viewjob?jk=87c76b5382d91ff5</t>
         </is>
       </c>
     </row>
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Augusta, ME, US USA</t>
+          <t>Pawtucket, RI, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,7 +4451,7 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e4b1fb8cf73679e</t>
+          <t>https://www.indeed.com/viewjob?jk=e2a46dfdabaf144b</t>
         </is>
       </c>
     </row>
@@ -4468,7 +4468,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>Hot Springs Village, AR, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eef37f19b519cfb3</t>
+          <t>https://www.indeed.com/viewjob?jk=148ea1e43d8803c0</t>
         </is>
       </c>
     </row>
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Jackson, MS, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2acd943bf9f49043</t>
+          <t>https://www.indeed.com/viewjob?jk=6d122abea15bffcd</t>
         </is>
       </c>
     </row>
@@ -4538,7 +4538,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Kansas City, KS, US USA</t>
+          <t>Middletown, DE, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4556,7 +4556,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b5356ec2fad3097c</t>
+          <t>https://www.indeed.com/viewjob?jk=b9fb52081cc83a1d</t>
         </is>
       </c>
     </row>
@@ -4573,7 +4573,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b0b088c77b432bf</t>
+          <t>https://www.indeed.com/viewjob?jk=6585b0f7548a110e</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Fremont, NH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4626,7 +4626,7 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=502c66caf2321daa</t>
+          <t>https://www.indeed.com/viewjob?jk=b6af657ad808aca0</t>
         </is>
       </c>
     </row>
@@ -4643,7 +4643,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Charleston, WV, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4661,7 +4661,7 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a8e35eb0472f1b04</t>
+          <t>https://www.indeed.com/viewjob?jk=8c71c57379755325</t>
         </is>
       </c>
     </row>
@@ -4678,7 +4678,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Okemos, MI, US USA</t>
+          <t>Augusta, ME, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ea808b55ddf87a1</t>
+          <t>https://www.indeed.com/viewjob?jk=6e4b1fb8cf73679e</t>
         </is>
       </c>
     </row>
@@ -4713,7 +4713,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4731,7 +4731,7 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8d2fb8ee058fcb4</t>
+          <t>https://www.indeed.com/viewjob?jk=eef37f19b519cfb3</t>
         </is>
       </c>
     </row>
@@ -4748,7 +4748,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=31e2d771ef37e989</t>
+          <t>https://www.indeed.com/viewjob?jk=2acd943bf9f49043</t>
         </is>
       </c>
     </row>
@@ -4783,7 +4783,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Corrales, NM, US USA</t>
+          <t>Kansas City, KS, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5701765b8810e954</t>
+          <t>https://www.indeed.com/viewjob?jk=b5356ec2fad3097c</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,7 +4836,7 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a74fc9df8466ed80</t>
+          <t>https://www.indeed.com/viewjob?jk=1b0b088c77b432bf</t>
         </is>
       </c>
     </row>
@@ -4853,7 +4853,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Upper Darby, PA, US USA</t>
+          <t>Fremont, NH, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e350cbedde8fb5c3</t>
+          <t>https://www.indeed.com/viewjob?jk=502c66caf2321daa</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,7 +4906,7 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37c3d1a6e3db03ea</t>
+          <t>https://www.indeed.com/viewjob?jk=a8e35eb0472f1b04</t>
         </is>
       </c>
     </row>
@@ -4923,7 +4923,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Okemos, MI, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3fb7cf0d3892b335</t>
+          <t>https://www.indeed.com/viewjob?jk=5ea808b55ddf87a1</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Oklahoma City, OK, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2515e91820622466</t>
+          <t>https://www.indeed.com/viewjob?jk=c8d2fb8ee058fcb4</t>
         </is>
       </c>
     </row>
@@ -4993,7 +4993,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Columbia, SC, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5011,7 +5011,7 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f92266e4f2da0ea</t>
+          <t>https://www.indeed.com/viewjob?jk=31e2d771ef37e989</t>
         </is>
       </c>
     </row>
@@ -5028,7 +5028,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Corrales, NM, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5834a6a46819e223</t>
+          <t>https://www.indeed.com/viewjob?jk=5701765b8810e954</t>
         </is>
       </c>
     </row>
@@ -5063,7 +5063,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>New Franken, WI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a21ae7255e004909</t>
+          <t>https://www.indeed.com/viewjob?jk=a74fc9df8466ed80</t>
         </is>
       </c>
     </row>
@@ -5098,7 +5098,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Upper Darby, PA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d766b034a172a2ae</t>
+          <t>https://www.indeed.com/viewjob?jk=e350cbedde8fb5c3</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Walnut Creek, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ab132d0ecb2e269</t>
+          <t>https://www.indeed.com/viewjob?jk=37c3d1a6e3db03ea</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,7 +5186,7 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=163d580eae60a657</t>
+          <t>https://www.indeed.com/viewjob?jk=3fb7cf0d3892b335</t>
         </is>
       </c>
     </row>
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>Oklahoma City, OK, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8c8d43b4208b386a</t>
+          <t>https://www.indeed.com/viewjob?jk=2515e91820622466</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Baton Rouge, LA, US USA</t>
+          <t>Columbia, SC, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58a509ab2ac2911c</t>
+          <t>https://www.indeed.com/viewjob?jk=9f92266e4f2da0ea</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=289f16a53bce28f8</t>
+          <t>https://www.indeed.com/viewjob?jk=5834a6a46819e223</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Whisker</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Auburn Hills, MI, US USA</t>
+          <t>New Franken, WI, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,112 +5316,112 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
+          <t>https://www.indeed.com/viewjob?jk=a21ae7255e004909</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
+          <t>https://www.indeed.com/viewjob?jk=d766b034a172a2ae</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Comcast</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>West Chester, PA, US USA</t>
+          <t>Walnut Creek, CA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
+          <t>https://www.indeed.com/viewjob?jk=3ab132d0ecb2e269</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Cloud Systems Engineer III</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Orange County's Credit Union</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Santa Ana, CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,32 +5431,32 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb076bf063bb2a72</t>
+          <t>https://www.indeed.com/viewjob?jk=163d580eae60a657</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Arrive Logistics</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,32 +5466,32 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4519eed0c0bcdda8</t>
+          <t>https://www.indeed.com/viewjob?jk=8c8d43b4208b386a</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior, Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Carrington Mortgage Services, LLC</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Baton Rouge, LA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,32 +5501,32 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=85cd0d74b3f6d1fd</t>
+          <t>https://www.indeed.com/viewjob?jk=58a509ab2ac2911c</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III - AI/ML Platform Operations - Remote</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Tiger Analytics</t>
+          <t>CSAA Insurance Group, a AAA Insurer</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala</t>
+          <t>AWS, RDS, Databricks, Scala, Splunk, MLOps, CI/CD, Jenkins, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
@@ -5536,59 +5536,59 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=06a5cdb578318149</t>
+          <t>https://www.indeed.com/viewjob?jk=289f16a53bce28f8</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Whisker</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Auburn Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, ETL, Python</t>
+          <t>AWS, Lambda, Kinesis, API Gateway, ECS, IAM, RDS, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ad4a5d391e5cb08</t>
+          <t>https://www.indeed.com/viewjob?jk=49e4025f9a54a6aa</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Data Engineer - (DataBricks, PySpark, AWS)</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>TrueScripts Management Services</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Washington, IN, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
+          <t>https://www.indeed.com/viewjob?jk=25ea972f667d3d3f</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Full Stack Engineer Senior / Infrastructure as Code / DBA</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Lockheed Martin</t>
+          <t>Comcast</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>King of Prussia, PA, US USA</t>
+          <t>West Chester, PA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, IAM, RDS, Azure, Oracle, SQL Server, CI/CD</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3382fc9be960cd51</t>
+          <t>https://www.indeed.com/viewjob?jk=1d8f7134bc1281d0</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Python/GenAI Solutions Architect</t>
+          <t>Cloud Systems Engineer III</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Provectus</t>
+          <t>Orange County's Credit Union</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Santa Ana, CA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Scala, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6ddb4f1cd1354de8</t>
+          <t>https://www.indeed.com/viewjob?jk=fb076bf063bb2a72</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Senior Enterprise Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Native American Industrial Solutions, LLC (NAIS)</t>
+          <t>Arrive Logistics</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,34 +5701,34 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
+          <t>Redshift, RDS, Azure, Databricks, BigQuery, Scala, Kafka, Snowflake, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
+          <t>https://www.indeed.com/viewjob?jk=4519eed0c0bcdda8</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior, Data Engineer</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Quantum Sky</t>
+          <t>Carrington Mortgage Services, LLC</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Wright-Patterson AFB, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,34 +5736,34 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, ETL, Microsoft SSIS</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
+          <t>https://www.indeed.com/viewjob?jk=85cd0d74b3f6d1fd</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sr Associate Engineer/Engineer, IT Software</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Tiger Analytics</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,34 +5771,34 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
+          <t>AWS, EMR, Redshift, Azure, Databricks, GCP, Hadoop, MapReduce, Spark, Scala</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
+          <t>https://www.indeed.com/viewjob?jk=06a5cdb578318149</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer - Platform Enablement</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Delinea</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Redwood City, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,17 +5806,17 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Spark, PySpark, Scala, ETL, Python</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
+          <t>https://www.indeed.com/viewjob?jk=8ad4a5d391e5cb08</t>
         </is>
       </c>
     </row>
@@ -5828,55 +5828,55 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>TrueScripts Management Services</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Washington, IN, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Data Modeling, ETL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, Scala, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ed0d719f5bbccf0</t>
+          <t>https://www.indeed.com/viewjob?jk=064eba971116911a</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Salt Lake City, UT, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Data Modeling, ETL</t>
+          <t>RDS, Google Cloud Platform, BigQuery, Scala, Kafka, Cassandra, Jenkins, Terraform, Docker, Jenkins</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,32 +5886,32 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=69ed747f2eb90e25</t>
+          <t>https://www.indeed.com/viewjob?jk=4c7248f02d82ed3a</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior Analytics Data Engineer - Homes.com</t>
+          <t>Python/GenAI Solutions Architect</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>CoStar Group</t>
+          <t>Provectus</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Power BI</t>
+          <t>AWS, Lambda, S3, SQS, ECS, RDS, GCP, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,137 +5921,137 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b80d45c896bb26ef</t>
+          <t>https://www.indeed.com/viewjob?jk=6ddb4f1cd1354de8</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II</t>
+          <t>Senior Enterprise Architect</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Bed Bath &amp; Beyond</t>
+          <t>Native American Industrial Solutions, LLC (NAIS)</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>Google Cloud Platform, Hadoop, HBase, Spark, Scala, Kafka, Cassandra, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Lambda, Kinesis, S3, SNS, IAM, RDS, Scala, Kafka, PostgreSQL</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e18063e9579ba86</t>
+          <t>https://www.indeed.com/viewjob?jk=8250689e965a0872</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Consumer Cellular</t>
+          <t>Quantum Sky</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Wright-Patterson AFB, OH, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, CI/CD, Jenkins, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dcea2f33a4118f28</t>
+          <t>https://www.indeed.com/viewjob?jk=6f6cc31f2ccc0f85</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Data Engineer- Greater Tampa</t>
+          <t>Sr Associate Engineer/Engineer, IT Software</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>MAXhealth</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
+          <t>AWS, RDS, Azure, Kafka, PostgreSQL, MongoDB, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
+          <t>https://www.indeed.com/viewjob?jk=3115e576ba7b5d84</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Copy of Software Engineer II, Data Platform</t>
+          <t>Senior Software Development Engineer - Platform Enablement</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>PlayStation</t>
+          <t>Delinea</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
+          <t>AWS, Azure, Scala, SQL Server, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
+          <t>https://www.indeed.com/viewjob?jk=cc904bf54c1e4425</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>NewYork-Presbyterian Hospital</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,34 +6086,34 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>2026-08-03</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf557823600dd122</t>
+          <t>https://www.indeed.com/viewjob?jk=7ed0d719f5bbccf0</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Software Engineer II (Backend, Platform)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Whoop</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Salt Lake City, UT, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Docker</t>
+          <t>AWS, Glue, Lambda, Athena, Step Functions, S3, RDS, Scala, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,67 +6131,67 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=145abebc67be2858</t>
+          <t>https://www.indeed.com/viewjob?jk=69ed747f2eb90e25</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Data Quality and Governance</t>
+          <t>Senior Analytics Data Engineer - Homes.com</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>CoStar Group</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, SQL Server, Power BI</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
+          <t>https://www.indeed.com/viewjob?jk=b80d45c896bb26ef</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Hertz</t>
+          <t>Consumer Cellular</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Estero, FL, US USA</t>
+          <t>Scottsdale, AZ, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Kafka, Snowflake, SQL Server, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,32 +6201,32 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3cb1b92b52d7a99</t>
+          <t>https://www.indeed.com/viewjob?jk=dcea2f33a4118f28</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Engineer- Greater Tampa</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>CLAIR</t>
+          <t>MAXhealth</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt, Airflow</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, SQL Server, Data Modeling, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,32 +6236,32 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62b06149f1d5d261</t>
+          <t>https://www.indeed.com/viewjob?jk=4ebc3cc20a81b9fe</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Copy of Software Engineer II, Data Platform</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>PlayStation</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, Kinesis, SQS, RDS, Databricks, GCP, Spark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,67 +6271,67 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
+          <t>https://www.indeed.com/viewjob?jk=fd6bead569945bd6</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Analytics Developer, Enterprise Analytics (Data Shared Services)</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Democratic National Committee</t>
+          <t>NewYork-Presbyterian Hospital</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Databricks, Google Cloud Platform, GCP, BigQuery, ETL, dbt, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Snowflake, Data Modeling, ELT, Power BI, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-03</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=17356bf4dd6cd564</t>
+          <t>https://www.indeed.com/viewjob?jk=cf557823600dd122</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Software Engineer II (Backend, Platform)</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>EPODIUM</t>
+          <t>Whoop</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Tacoma, WA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Docker</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7bacca274417a8a0</t>
+          <t>https://www.indeed.com/viewjob?jk=145abebc67be2858</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Payments IT Business Analyst (AI &amp; Data Focus)</t>
+          <t>Senior Data Engineer - Data Quality and Governance</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>MUFG</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,34 +6366,34 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Power BI, Tableau</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Oracle, SQL Server, CI/CD, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e859637db4511ad</t>
+          <t>https://www.indeed.com/viewjob?jk=f9fa3bf81f33a87f</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Systems Administrator</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Pacific Consulting</t>
+          <t>Hertz</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Salem, VA, US USA</t>
+          <t>Estero, FL, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, SQL</t>
+          <t>AWS, Kinesis, Azure, Databricks, Medallion Architecture, Spark, PySpark, Scala, Kafka, ETL</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e8bd5938a7b9489</t>
+          <t>https://www.indeed.com/viewjob?jk=c3cb1b92b52d7a99</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Alliance Health Plan</t>
+          <t>CLAIR</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Morrisville, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
+          <t>Redshift, RDS, BigQuery, Snowflake, Data Modeling, Dimensional Modeling, Kimball, ELT, dbt, Airflow</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
+          <t>https://www.indeed.com/viewjob?jk=62b06149f1d5d261</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Goldman Sachs</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d45183e5b3bce9f1</t>
+          <t>https://www.indeed.com/viewjob?jk=6d539c21d8a7cb01</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>VIE - Software Engineer (based in Miami)</t>
+          <t>Systems Administrator</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Pelico</t>
+          <t>EPODIUM</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Tacoma, WA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=072180860b5c5965</t>
+          <t>https://www.indeed.com/viewjob?jk=7bacca274417a8a0</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior Payments IT Business Analyst (AI &amp; Data Focus)</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>MUFG</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,15 +6541,260 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Kafka, Snowflake, Power BI, Tableau</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6e859637db4511ad</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Full Stack Developer (need only locals)</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=78002654e3f6aec5</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Systems Administrator</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Pacific Consulting</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Salem, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, SQL</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0e8bd5938a7b9489</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Dir-Data Platform Engineering (Full-time Remote, North Carolina Based)</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Alliance Health Plan</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Morrisville, NC, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ebdf670f668b0e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Senior Analytics Engineer II</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Wrapbook</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Redshift, RDS, Databricks, Snowflake, Data Modeling, ETL, ELT, dbt, Tableau, CI/CD</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c920b57c72b89cab</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>VIE - Software Engineer (based in Miami)</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Pelico</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2025-10-07</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=072180860b5c5965</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Engineering-L2-Dallas-Analyst-Software Engineering</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Goldman Sachs</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Dallas, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Hadoop, Spark, Scala, Kafka, Snowflake, CI/CD, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d45183e5b3bce9f1</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Engineer/Sr Engineer, IT Software</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>American Airlines</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
           <t>RDS, Azure, Databricks, Kafka, PostgreSQL, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
-      <c r="F175" t="inlineStr">
+      <c r="F182" t="inlineStr">
         <is>
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="G175" t="inlineStr">
+      <c r="G182" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=1ed393ac81f7cc7f</t>
         </is>
